--- a/Tables/MAIHDA Tables_10-03-26.xlsx
+++ b/Tables/MAIHDA Tables_10-03-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38b97e870d12de33/Documents/UAH/PhD Documents/INEdatos/Analysis/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="11_F25DC773A252ABDACC10487F095D4F545ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23F6E16A-F7E4-49A8-AAAF-ADC938C2F740}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="11_F25DC773A252ABDACC10487F095D4F545ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35454E1A-84C0-4B90-8C44-209C04FD82F7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="4" r:id="rId1"/>
@@ -971,6 +971,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1007,14 +1010,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
@@ -1035,9 +1038,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <fill>
@@ -1080,7 +1080,7 @@
     <tableColumn id="5" xr3:uid="{9DAD0F1A-F3F6-44A3-B51F-5A354204DC9D}" name="urb_rur"/>
     <tableColumn id="7" xr3:uid="{D3F4A0C7-1C81-4C71-89B6-BD2D16036EEB}" name="survey2"/>
     <tableColumn id="8" xr3:uid="{D3999EC7-8E08-4D99-B740-82D6BEFF4325}" name="sedentarismo2"/>
-    <tableColumn id="25" xr3:uid="{D24E67DF-6897-48FC-9865-6FF9A8E85265}" name="sedentarismo3" dataDxfId="0">
+    <tableColumn id="25" xr3:uid="{D24E67DF-6897-48FC-9865-6FF9A8E85265}" name="sedentarismo3" dataDxfId="3">
       <calculatedColumnFormula>Table3[[#This Row],[sedentarismo2]]*100</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{E1D21D91-DCFD-48C5-864D-CF96A73456D4}" name="m0_prob_total"/>
@@ -1089,9 +1089,9 @@
     <tableColumn id="12" xr3:uid="{D5C15FB5-37C2-41D7-8160-B9D083AF964B}" name="m1fit_fixed"/>
     <tableColumn id="13" xr3:uid="{14A66936-1DEC-450B-B497-9444AECD70FB}" name="m1upr_fixed"/>
     <tableColumn id="14" xr3:uid="{50BFCDC3-6099-4F99-9A76-75DF7B4FB1A3}" name="m1lwr_fixed"/>
-    <tableColumn id="15" xr3:uid="{C2E3473C-9D24-46B8-8905-23494831E784}" name="m1fit_total" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{6399EEB5-7946-4AB9-AD9F-78570C2DF974}" name="m1lwr_total" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{6A3714D1-62BF-4525-AB2F-3A644421021F}" name="m1upr_total" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{C2E3473C-9D24-46B8-8905-23494831E784}" name="m1fit_total" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{6399EEB5-7946-4AB9-AD9F-78570C2DF974}" name="m1lwr_total" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{6A3714D1-62BF-4525-AB2F-3A644421021F}" name="m1upr_total" dataDxfId="0"/>
     <tableColumn id="18" xr3:uid="{70EE4036-E7FB-4F16-9FB9-B2F45AAED60A}" name="se_total"/>
     <tableColumn id="19" xr3:uid="{66F1F112-5D13-422E-952E-C9FAB9D6098A}" name="se_fixed"/>
     <tableColumn id="20" xr3:uid="{1A7C1E61-677A-48E2-B79F-673A6C0D031F}" name="se_diff"/>
@@ -1428,26 +1428,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30493F8C-7541-4087-8756-547165D1DA7B}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.77734375" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="31"/>
       <c r="D1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="32"/>
       <c r="D2">
         <v>1</v>
       </c>
@@ -1551,11 +1551,11 @@
         <v>1</v>
       </c>
       <c r="G10" s="24">
-        <f>H10*100</f>
+        <f t="shared" ref="G10:G24" si="0">H10*100</f>
         <v>1.3888888888888888</v>
       </c>
       <c r="H10">
-        <f>F10/72</f>
+        <f t="shared" ref="H10:H24" si="1">F10/72</f>
         <v>1.3888888888888888E-2</v>
       </c>
     </row>
@@ -1571,11 +1571,11 @@
         <v>7</v>
       </c>
       <c r="G11" s="24">
-        <f>H11*100</f>
+        <f t="shared" si="0"/>
         <v>9.7222222222222232</v>
       </c>
       <c r="H11">
-        <f>F11/72</f>
+        <f t="shared" si="1"/>
         <v>9.7222222222222224E-2</v>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>11</v>
       </c>
       <c r="G12" s="24">
-        <f>H12*100</f>
+        <f t="shared" si="0"/>
         <v>15.277777777777779</v>
       </c>
       <c r="H12">
-        <f>F12/72</f>
+        <f t="shared" si="1"/>
         <v>0.15277777777777779</v>
       </c>
     </row>
@@ -1615,11 +1615,11 @@
         <v>13</v>
       </c>
       <c r="G13" s="24">
-        <f>H13*100</f>
+        <f t="shared" si="0"/>
         <v>18.055555555555554</v>
       </c>
       <c r="H13">
-        <f>F13/72</f>
+        <f t="shared" si="1"/>
         <v>0.18055555555555555</v>
       </c>
     </row>
@@ -1637,11 +1637,11 @@
         <v>18</v>
       </c>
       <c r="G14" s="24">
-        <f>H14*100</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="H14">
-        <f>F14/72</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
     </row>
@@ -1657,11 +1657,11 @@
         <v>27</v>
       </c>
       <c r="G15" s="24">
-        <f>H15*100</f>
+        <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
       <c r="H15">
-        <f>F15/72</f>
+        <f t="shared" si="1"/>
         <v>0.375</v>
       </c>
     </row>
@@ -1679,11 +1679,11 @@
         <v>35</v>
       </c>
       <c r="G16" s="24">
-        <f>H16*100</f>
+        <f t="shared" si="0"/>
         <v>48.611111111111107</v>
       </c>
       <c r="H16">
-        <f>F16/72</f>
+        <f t="shared" si="1"/>
         <v>0.4861111111111111</v>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>48</v>
       </c>
       <c r="G17" s="24">
-        <f>H17*100</f>
+        <f t="shared" si="0"/>
         <v>66.666666666666657</v>
       </c>
       <c r="H17">
-        <f>F17/72</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -1721,11 +1721,11 @@
         <v>52</v>
       </c>
       <c r="G18" s="24">
-        <f>H18*100</f>
+        <f t="shared" si="0"/>
         <v>72.222222222222214</v>
       </c>
       <c r="H18">
-        <f>F18/72</f>
+        <f t="shared" si="1"/>
         <v>0.72222222222222221</v>
       </c>
     </row>
@@ -1743,11 +1743,11 @@
         <v>56</v>
       </c>
       <c r="G19" s="24">
-        <f>H19*100</f>
+        <f t="shared" si="0"/>
         <v>77.777777777777786</v>
       </c>
       <c r="H19">
-        <f>F19/72</f>
+        <f t="shared" si="1"/>
         <v>0.77777777777777779</v>
       </c>
     </row>
@@ -1765,11 +1765,11 @@
         <v>66</v>
       </c>
       <c r="G20" s="24">
-        <f>H20*100</f>
+        <f t="shared" si="0"/>
         <v>91.666666666666657</v>
       </c>
       <c r="H20">
-        <f>F20/72</f>
+        <f t="shared" si="1"/>
         <v>0.91666666666666663</v>
       </c>
     </row>
@@ -1785,11 +1785,11 @@
         <v>66</v>
       </c>
       <c r="G21" s="24">
-        <f>H21*100</f>
+        <f t="shared" si="0"/>
         <v>91.666666666666657</v>
       </c>
       <c r="H21">
-        <f>F21/72</f>
+        <f t="shared" si="1"/>
         <v>0.91666666666666663</v>
       </c>
     </row>
@@ -1807,11 +1807,11 @@
         <v>67</v>
       </c>
       <c r="G22" s="24">
-        <f>H22*100</f>
+        <f t="shared" si="0"/>
         <v>93.055555555555557</v>
       </c>
       <c r="H22">
-        <f>F22/72</f>
+        <f t="shared" si="1"/>
         <v>0.93055555555555558</v>
       </c>
     </row>
@@ -1829,19 +1829,19 @@
         <v>69</v>
       </c>
       <c r="G23" s="24">
-        <f>H23*100</f>
+        <f t="shared" si="0"/>
         <v>95.833333333333343</v>
       </c>
       <c r="H23">
-        <f>F23/72</f>
+        <f t="shared" si="1"/>
         <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="30"/>
+      <c r="B24" s="33"/>
       <c r="D24" t="s">
         <v>164</v>
       </c>
@@ -1849,11 +1849,11 @@
         <v>72</v>
       </c>
       <c r="G24" s="24">
-        <f>H24*100</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H24">
-        <f>F24/72</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DC0C2D-CA39-42D0-AAFA-943778B10C90}">
   <dimension ref="A1:E67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" customWidth="1"/>
@@ -1888,11 +1888,11 @@
     </row>
     <row r="2" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
@@ -1923,72 +1923,72 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
     </row>
     <row r="6" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="40">
         <v>3.29</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="40">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="40">
         <v>0.08</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
     </row>
     <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="42">
         <v>72</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="39">
         <v>19503</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
     </row>
     <row r="11" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -2021,11 +2021,11 @@
     </row>
     <row r="18" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
     </row>
     <row r="19" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
@@ -2154,85 +2154,85 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
     </row>
     <row r="29" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="34">
         <v>3.29</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="34">
         <v>0.03</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="22"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="34">
         <v>0.01</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="22"/>
     </row>
     <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="35">
         <v>72</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="36">
         <v>19503</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
     </row>
     <row r="34" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="38">
         <v>7.9442479999999992E-3</v>
       </c>
-      <c r="C36" s="35"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="8">
         <v>0.79442480000000004</v>
       </c>
@@ -2383,78 +2383,78 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="34"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
     </row>
     <row r="51" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="34">
         <v>3.29</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31">
+      <c r="C51" s="34"/>
+      <c r="D51" s="34">
         <v>3.29</v>
       </c>
-      <c r="E51" s="31"/>
+      <c r="E51" s="34"/>
     </row>
     <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31" t="s">
+      <c r="C52" s="34"/>
+      <c r="D52" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="31"/>
+      <c r="E52" s="34"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B53" s="31">
+      <c r="B53" s="34">
         <v>0.08</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31">
+      <c r="C53" s="34"/>
+      <c r="D53" s="34">
         <v>0.01</v>
       </c>
-      <c r="E53" s="31"/>
+      <c r="E53" s="34"/>
     </row>
     <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32" t="s">
+      <c r="C54" s="35"/>
+      <c r="D54" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="E54" s="32"/>
+      <c r="E54" s="35"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B55" s="33">
+      <c r="B55" s="36">
         <v>19500</v>
       </c>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33">
+      <c r="C55" s="36"/>
+      <c r="D55" s="36">
         <v>19500</v>
       </c>
-      <c r="E55" s="33"/>
+      <c r="E55" s="36"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="27" t="s">
@@ -2568,7 +2568,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE5C60F-1F9A-44BA-B029-B52BD23DE95C}">
   <dimension ref="A1:C74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3383,7 +3383,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B49F686-15BB-461D-9535-4954B854B5B7}">
   <dimension ref="A1:AP73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
     <col min="2" max="2" width="9.21875" customWidth="1"/>
@@ -3391,12 +3391,12 @@
     <col min="5" max="5" width="9.21875" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="8" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="16" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="13.88671875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" customWidth="1"/>
     <col min="16" max="16" width="13.77734375" customWidth="1"/>
     <col min="17" max="17" width="13.44140625" customWidth="1"/>
     <col min="18" max="18" width="12.5546875" customWidth="1"/>
@@ -3514,7 +3514,7 @@
       <c r="H2" s="1">
         <v>0.04</v>
       </c>
-      <c r="I2" s="40">
+      <c r="I2" s="28">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>4</v>
       </c>
@@ -3536,13 +3536,13 @@
       <c r="O2" s="1">
         <v>3.6792996726757101</v>
       </c>
-      <c r="P2" s="40">
+      <c r="P2" s="28">
         <v>4.3948023549232103</v>
       </c>
-      <c r="Q2" s="40">
+      <c r="Q2" s="28">
         <v>3.0790492987424001</v>
       </c>
-      <c r="R2" s="40">
+      <c r="R2" s="28">
         <v>6.2879308949180102</v>
       </c>
       <c r="S2" s="1">
@@ -3637,7 +3637,7 @@
       <c r="H3" s="1">
         <v>4.9382716049382699E-2</v>
       </c>
-      <c r="I3" s="40">
+      <c r="I3" s="28">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>4.9382716049382696</v>
       </c>
@@ -3659,13 +3659,13 @@
       <c r="O3" s="1">
         <v>3.8215099904382601</v>
       </c>
-      <c r="P3" s="40">
+      <c r="P3" s="28">
         <v>4.6605319118195103</v>
       </c>
-      <c r="Q3" s="40">
+      <c r="Q3" s="28">
         <v>3.2469437321692798</v>
       </c>
-      <c r="R3" s="40">
+      <c r="R3" s="28">
         <v>6.5388855628519096</v>
       </c>
       <c r="S3" s="1">
@@ -3760,7 +3760,7 @@
       <c r="H4" s="1">
         <v>2.6490066225165601E-2</v>
       </c>
-      <c r="I4" s="40">
+      <c r="I4" s="28">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>2.64900662251656</v>
       </c>
@@ -3782,13 +3782,13 @@
       <c r="O4" s="1">
         <v>4.9614484364900697</v>
       </c>
-      <c r="P4" s="40">
+      <c r="P4" s="28">
         <v>5.2448626718628999</v>
       </c>
-      <c r="Q4" s="40">
+      <c r="Q4" s="28">
         <v>3.6908498038225299</v>
       </c>
-      <c r="R4" s="40">
+      <c r="R4" s="28">
         <v>7.2622988466452396</v>
       </c>
       <c r="S4" s="1">
@@ -3883,7 +3883,7 @@
       <c r="H5" s="1">
         <v>5.7591623036649199E-2</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="28">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>5.7591623036649198</v>
       </c>
@@ -3905,13 +3905,13 @@
       <c r="O5" s="1">
         <v>5.0717177351993001</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="28">
         <v>5.9543551884185</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="28">
         <v>4.3816060108922699</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="28">
         <v>8.0923805661354198</v>
       </c>
       <c r="S5" s="1">
@@ -4006,7 +4006,7 @@
       <c r="H6" s="1">
         <v>6.3745019920318696E-2</v>
       </c>
-      <c r="I6" s="40">
+      <c r="I6" s="28">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>6.3745019920318695</v>
       </c>
@@ -4028,13 +4028,13 @@
       <c r="O6" s="1">
         <v>5.2755932874915104</v>
       </c>
-      <c r="P6" s="40">
+      <c r="P6" s="28">
         <v>6.2708159128190104</v>
       </c>
-      <c r="Q6" s="40">
+      <c r="Q6" s="28">
         <v>4.5498262836387102</v>
       </c>
-      <c r="R6" s="40">
+      <c r="R6" s="28">
         <v>8.3049287466320401</v>
       </c>
       <c r="S6" s="1">
@@ -4129,7 +4129,7 @@
       <c r="H7">
         <v>8.0291970802919693E-2</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.0291970802919685</v>
       </c>
@@ -4151,13 +4151,13 @@
       <c r="O7">
         <v>5.1111308871738999</v>
       </c>
-      <c r="P7" s="41">
+      <c r="P7" s="29">
         <v>6.3338383836364898</v>
       </c>
-      <c r="Q7" s="41">
+      <c r="Q7" s="29">
         <v>4.6188173522968103</v>
       </c>
-      <c r="R7" s="41">
+      <c r="R7" s="29">
         <v>8.8108069553503192</v>
       </c>
       <c r="S7">
@@ -4252,7 +4252,7 @@
       <c r="H8">
         <v>7.9847908745247206E-2</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>7.9847908745247205</v>
       </c>
@@ -4274,13 +4274,13 @@
       <c r="O8">
         <v>4.8577944827163</v>
       </c>
-      <c r="P8" s="41">
+      <c r="P8" s="29">
         <v>6.4898289866617</v>
       </c>
-      <c r="Q8" s="41">
+      <c r="Q8" s="29">
         <v>4.6678759333899098</v>
       </c>
-      <c r="R8" s="41">
+      <c r="R8" s="29">
         <v>8.5568571144555605</v>
       </c>
       <c r="S8">
@@ -4330,7 +4330,7 @@
       <c r="H9">
         <v>8.2089552238805999E-2</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.2089552238806007</v>
       </c>
@@ -4352,13 +4352,13 @@
       <c r="O9">
         <v>5.0775490528240201</v>
       </c>
-      <c r="P9" s="41">
+      <c r="P9" s="29">
         <v>6.6296564240080098</v>
       </c>
-      <c r="Q9" s="41">
+      <c r="Q9" s="29">
         <v>4.9146103851837104</v>
       </c>
-      <c r="R9" s="41">
+      <c r="R9" s="29">
         <v>9.1253515678154997</v>
       </c>
       <c r="S9">
@@ -4411,7 +4411,7 @@
       <c r="H10">
         <v>3.2258064516128997E-2</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>3.2258064516128995</v>
       </c>
@@ -4433,13 +4433,13 @@
       <c r="O10">
         <v>5.9263817822864402</v>
       </c>
-      <c r="P10" s="41">
+      <c r="P10" s="29">
         <v>6.7303037205599603</v>
       </c>
-      <c r="Q10" s="41">
+      <c r="Q10" s="29">
         <v>4.8626925274357999</v>
       </c>
-      <c r="R10" s="41">
+      <c r="R10" s="29">
         <v>9.4065096481583605</v>
       </c>
       <c r="S10">
@@ -4534,7 +4534,7 @@
       <c r="H11">
         <v>9.5238095238095205E-2</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>9.5238095238095202</v>
       </c>
@@ -4556,13 +4556,13 @@
       <c r="O11">
         <v>5.9337208829947503</v>
       </c>
-      <c r="P11" s="41">
+      <c r="P11" s="29">
         <v>7.50547685894953</v>
       </c>
-      <c r="Q11" s="41">
+      <c r="Q11" s="29">
         <v>5.5115131909580803</v>
       </c>
-      <c r="R11" s="41">
+      <c r="R11" s="29">
         <v>10.173241400972501</v>
       </c>
       <c r="S11">
@@ -4657,7 +4657,7 @@
       <c r="H12">
         <v>8.8435374149659907E-2</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.84353741496599</v>
       </c>
@@ -4679,13 +4679,13 @@
       <c r="O12">
         <v>6.14783094145489</v>
       </c>
-      <c r="P12" s="41">
+      <c r="P12" s="29">
         <v>7.61905073763596</v>
       </c>
-      <c r="Q12" s="41">
+      <c r="Q12" s="29">
         <v>5.3919783387826099</v>
       </c>
-      <c r="R12" s="41">
+      <c r="R12" s="29">
         <v>10.2926568038482</v>
       </c>
       <c r="S12">
@@ -4780,7 +4780,7 @@
       <c r="H13">
         <v>2.5974025974026E-2</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>2.5974025974026</v>
       </c>
@@ -4802,13 +4802,13 @@
       <c r="O13">
         <v>7.0983450716512904</v>
       </c>
-      <c r="P13" s="41">
+      <c r="P13" s="29">
         <v>7.6645798961193696</v>
       </c>
-      <c r="Q13" s="41">
+      <c r="Q13" s="29">
         <v>5.3464073186295202</v>
       </c>
-      <c r="R13" s="41">
+      <c r="R13" s="29">
         <v>10.760805833405101</v>
       </c>
       <c r="S13">
@@ -4903,7 +4903,7 @@
       <c r="H14">
         <v>4.47761194029851E-2</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>4.4776119402985097</v>
       </c>
@@ -4925,13 +4925,13 @@
       <c r="O14">
         <v>6.8491759323565899</v>
       </c>
-      <c r="P14" s="41">
+      <c r="P14" s="29">
         <v>7.6858251657161896</v>
       </c>
-      <c r="Q14" s="41">
+      <c r="Q14" s="29">
         <v>5.4745692130650498</v>
       </c>
-      <c r="R14" s="41">
+      <c r="R14" s="29">
         <v>10.865233527947099</v>
       </c>
       <c r="S14">
@@ -5026,7 +5026,7 @@
       <c r="H15">
         <v>7.8260869565217397E-2</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>7.8260869565217401</v>
       </c>
@@ -5048,13 +5048,13 @@
       <c r="O15">
         <v>6.6902601110509696</v>
       </c>
-      <c r="P15" s="41">
+      <c r="P15" s="29">
         <v>7.8412026019208803</v>
       </c>
-      <c r="Q15" s="41">
+      <c r="Q15" s="29">
         <v>5.8691551625586804</v>
       </c>
-      <c r="R15" s="41">
+      <c r="R15" s="29">
         <v>10.379450366012099</v>
       </c>
       <c r="S15">
@@ -5149,7 +5149,7 @@
       <c r="H16">
         <v>8.0971659919028299E-2</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.0971659919028305</v>
       </c>
@@ -5171,13 +5171,13 @@
       <c r="O16">
         <v>6.9900578245045297</v>
       </c>
-      <c r="P16" s="41">
+      <c r="P16" s="29">
         <v>8.0464684132235007</v>
       </c>
-      <c r="Q16" s="41">
+      <c r="Q16" s="29">
         <v>6.1922846105188203</v>
       </c>
-      <c r="R16" s="41">
+      <c r="R16" s="29">
         <v>10.255263744314201</v>
       </c>
       <c r="S16">
@@ -5227,7 +5227,7 @@
       <c r="H17">
         <v>8.6876155268022198E-2</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.6876155268022206</v>
       </c>
@@ -5249,13 +5249,13 @@
       <c r="O17">
         <v>6.6244495852426404</v>
       </c>
-      <c r="P17" s="41">
+      <c r="P17" s="29">
         <v>8.1931652813888398</v>
       </c>
-      <c r="Q17" s="41">
+      <c r="Q17" s="29">
         <v>6.4041968630764101</v>
       </c>
-      <c r="R17" s="41">
+      <c r="R17" s="29">
         <v>10.598906233207501</v>
       </c>
       <c r="S17">
@@ -5305,7 +5305,7 @@
       <c r="H18">
         <v>0.101123595505618</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.1123595505618</v>
       </c>
@@ -5327,13 +5327,13 @@
       <c r="O18">
         <v>6.4389293778116503</v>
       </c>
-      <c r="P18" s="41">
+      <c r="P18" s="29">
         <v>8.3228690054973598</v>
       </c>
-      <c r="Q18" s="41">
+      <c r="Q18" s="29">
         <v>6.3535697055454898</v>
       </c>
-      <c r="R18" s="41">
+      <c r="R18" s="29">
         <v>10.9980072868722</v>
       </c>
       <c r="S18">
@@ -5383,7 +5383,7 @@
       <c r="H19">
         <v>6.6666666666666693E-2</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>6.6666666666666696</v>
       </c>
@@ -5405,13 +5405,13 @@
       <c r="O19">
         <v>8.0406184109237504</v>
       </c>
-      <c r="P19" s="41">
+      <c r="P19" s="29">
         <v>8.4035574211936304</v>
       </c>
-      <c r="Q19" s="41">
+      <c r="Q19" s="29">
         <v>6.4948246040623303</v>
       </c>
-      <c r="R19" s="41">
+      <c r="R19" s="29">
         <v>11.069919595773399</v>
       </c>
       <c r="S19">
@@ -5461,7 +5461,7 @@
       <c r="H20">
         <v>8.1081081081081099E-2</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.1081081081081106</v>
       </c>
@@ -5483,13 +5483,13 @@
       <c r="O20">
         <v>7.7808982862016496</v>
       </c>
-      <c r="P20" s="41">
+      <c r="P20" s="29">
         <v>8.7814571136506796</v>
       </c>
-      <c r="Q20" s="41">
+      <c r="Q20" s="29">
         <v>6.5895520957236204</v>
       </c>
-      <c r="R20" s="41">
+      <c r="R20" s="29">
         <v>11.802730062655799</v>
       </c>
       <c r="S20">
@@ -5539,7 +5539,7 @@
       <c r="H21">
         <v>8.5714285714285701E-2</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>8.5714285714285694</v>
       </c>
@@ -5561,13 +5561,13 @@
       <c r="O21">
         <v>7.7193265310677903</v>
       </c>
-      <c r="P21" s="41">
+      <c r="P21" s="29">
         <v>8.8606337262394703</v>
       </c>
-      <c r="Q21" s="41">
+      <c r="Q21" s="29">
         <v>6.5932613495769896</v>
       </c>
-      <c r="R21" s="41">
+      <c r="R21" s="29">
         <v>11.7677414738321</v>
       </c>
       <c r="S21">
@@ -5617,7 +5617,7 @@
       <c r="H22">
         <v>0.104477611940299</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.4477611940299</v>
       </c>
@@ -5639,13 +5639,13 @@
       <c r="O22">
         <v>7.7525764987789296</v>
       </c>
-      <c r="P22" s="41">
+      <c r="P22" s="29">
         <v>9.4796169746231698</v>
       </c>
-      <c r="Q22" s="41">
+      <c r="Q22" s="29">
         <v>7.1334534829244598</v>
       </c>
-      <c r="R22" s="41">
+      <c r="R22" s="29">
         <v>12.7098400836928</v>
       </c>
       <c r="S22">
@@ -5695,7 +5695,7 @@
       <c r="H23">
         <v>6.25E-2</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>6.25</v>
       </c>
@@ -5717,13 +5717,13 @@
       <c r="O23">
         <v>9.0587117934050401</v>
       </c>
-      <c r="P23" s="41">
+      <c r="P23" s="29">
         <v>9.5502015800403601</v>
       </c>
-      <c r="Q23" s="41">
+      <c r="Q23" s="29">
         <v>6.88077538496883</v>
       </c>
-      <c r="R23" s="41">
+      <c r="R23" s="29">
         <v>13.040416335641799</v>
       </c>
       <c r="S23">
@@ -5773,7 +5773,7 @@
       <c r="H24">
         <v>0.11214953271028</v>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>11.214953271028</v>
       </c>
@@ -5795,13 +5795,13 @@
       <c r="O24">
         <v>7.82763470277055</v>
       </c>
-      <c r="P24" s="41">
+      <c r="P24" s="29">
         <v>9.5604568791387408</v>
       </c>
-      <c r="Q24" s="41">
+      <c r="Q24" s="29">
         <v>7.0193394613628897</v>
       </c>
-      <c r="R24" s="41">
+      <c r="R24" s="29">
         <v>13.0464134719426</v>
       </c>
       <c r="S24">
@@ -5851,7 +5851,7 @@
       <c r="H25">
         <v>6.3380281690140802E-2</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>6.3380281690140805</v>
       </c>
@@ -5873,13 +5873,13 @@
       <c r="O25">
         <v>9.3953375460259902</v>
       </c>
-      <c r="P25" s="41">
+      <c r="P25" s="29">
         <v>9.5735614362485606</v>
       </c>
-      <c r="Q25" s="41">
+      <c r="Q25" s="29">
         <v>6.9974166687335</v>
       </c>
-      <c r="R25" s="41">
+      <c r="R25" s="29">
         <v>13.092074945368999</v>
       </c>
       <c r="S25">
@@ -5929,7 +5929,7 @@
       <c r="H26">
         <v>9.7902097902097904E-2</v>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>9.79020979020979</v>
       </c>
@@ -5951,13 +5951,13 @@
       <c r="O26">
         <v>8.4023043952491694</v>
       </c>
-      <c r="P26" s="41">
+      <c r="P26" s="29">
         <v>9.6629344789176006</v>
       </c>
-      <c r="Q26" s="41">
+      <c r="Q26" s="29">
         <v>7.3079849559047201</v>
       </c>
-      <c r="R26" s="41">
+      <c r="R26" s="29">
         <v>12.639221200579801</v>
       </c>
       <c r="S26">
@@ -6007,7 +6007,7 @@
       <c r="H27">
         <v>7.4175824175824204E-2</v>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>7.4175824175824205</v>
       </c>
@@ -6029,13 +6029,13 @@
       <c r="O27">
         <v>10.409331225157199</v>
       </c>
-      <c r="P27" s="41">
+      <c r="P27" s="29">
         <v>9.8200382469118797</v>
       </c>
-      <c r="Q27" s="41">
+      <c r="Q27" s="29">
         <v>7.5735875970533204</v>
       </c>
-      <c r="R27" s="41">
+      <c r="R27" s="29">
         <v>12.5741105587257</v>
       </c>
       <c r="S27">
@@ -6085,7 +6085,7 @@
       <c r="H28">
         <v>0.10423452768729601</v>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.4234527687296</v>
       </c>
@@ -6107,13 +6107,13 @@
       <c r="O28">
         <v>8.0193333013304695</v>
       </c>
-      <c r="P28" s="41">
+      <c r="P28" s="29">
         <v>9.8608726160201403</v>
       </c>
-      <c r="Q28" s="41">
+      <c r="Q28" s="29">
         <v>7.4586030912682499</v>
       </c>
-      <c r="R28" s="41">
+      <c r="R28" s="29">
         <v>12.7451821703246</v>
       </c>
       <c r="S28">
@@ -6163,7 +6163,7 @@
       <c r="H29">
         <v>7.03125E-2</v>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>7.03125</v>
       </c>
@@ -6185,13 +6185,13 @@
       <c r="O29">
         <v>9.3476837313433307</v>
       </c>
-      <c r="P29" s="41">
+      <c r="P29" s="29">
         <v>10.1171424397088</v>
       </c>
-      <c r="Q29" s="41">
+      <c r="Q29" s="29">
         <v>7.3811300935536899</v>
       </c>
-      <c r="R29" s="41">
+      <c r="R29" s="29">
         <v>13.3506063291928</v>
       </c>
       <c r="S29">
@@ -6241,7 +6241,7 @@
       <c r="H30">
         <v>0.1</v>
       </c>
-      <c r="I30" s="41">
+      <c r="I30" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10</v>
       </c>
@@ -6263,13 +6263,13 @@
       <c r="O30">
         <v>8.8999901649061304</v>
       </c>
-      <c r="P30" s="41">
+      <c r="P30" s="29">
         <v>10.319961451454899</v>
       </c>
-      <c r="Q30" s="41">
+      <c r="Q30" s="29">
         <v>7.7253451270140099</v>
       </c>
-      <c r="R30" s="41">
+      <c r="R30" s="29">
         <v>13.541029612820299</v>
       </c>
       <c r="S30">
@@ -6319,7 +6319,7 @@
       <c r="H31">
         <v>9.8113207547169803E-2</v>
       </c>
-      <c r="I31" s="41">
+      <c r="I31" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>9.8113207547169807</v>
       </c>
@@ -6341,13 +6341,13 @@
       <c r="O31">
         <v>9.3173048310203992</v>
       </c>
-      <c r="P31" s="41">
+      <c r="P31" s="29">
         <v>10.454667381712399</v>
       </c>
-      <c r="Q31" s="41">
+      <c r="Q31" s="29">
         <v>7.8536698382389698</v>
       </c>
-      <c r="R31" s="41">
+      <c r="R31" s="29">
         <v>13.5813023961762</v>
       </c>
       <c r="S31">
@@ -6397,7 +6397,7 @@
       <c r="H32">
         <v>0.102459016393443</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.2459016393443</v>
       </c>
@@ -6419,13 +6419,13 @@
       <c r="O32">
         <v>9.6232129847333905</v>
       </c>
-      <c r="P32" s="41">
+      <c r="P32" s="29">
         <v>10.8163791150679</v>
       </c>
-      <c r="Q32" s="41">
+      <c r="Q32" s="29">
         <v>8.1068517749095292</v>
       </c>
-      <c r="R32" s="41">
+      <c r="R32" s="29">
         <v>14.088460785638</v>
       </c>
       <c r="S32">
@@ -6475,7 +6475,7 @@
       <c r="H33">
         <v>0.10462776659959799</v>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.462776659959799</v>
       </c>
@@ -6497,13 +6497,13 @@
       <c r="O33">
         <v>10.5564023512917</v>
       </c>
-      <c r="P33" s="41">
+      <c r="P33" s="29">
         <v>11.116032001734901</v>
       </c>
-      <c r="Q33" s="41">
+      <c r="Q33" s="29">
         <v>8.8136306605724108</v>
       </c>
-      <c r="R33" s="41">
+      <c r="R33" s="29">
         <v>14.009822753325301</v>
       </c>
       <c r="S33">
@@ -6553,7 +6553,7 @@
       <c r="H34">
         <v>9.5330739299610903E-2</v>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>9.5330739299610912</v>
       </c>
@@ -6575,13 +6575,13 @@
       <c r="O34">
         <v>12.065718421533999</v>
       </c>
-      <c r="P34" s="41">
+      <c r="P34" s="29">
         <v>11.315087987982301</v>
       </c>
-      <c r="Q34" s="41">
+      <c r="Q34" s="29">
         <v>8.9068747808792104</v>
       </c>
-      <c r="R34" s="41">
+      <c r="R34" s="29">
         <v>14.0193221350365</v>
       </c>
       <c r="S34">
@@ -6631,7 +6631,7 @@
       <c r="H35">
         <v>0.105675146771037</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.5675146771037</v>
       </c>
@@ -6653,13 +6653,13 @@
       <c r="O35">
         <v>10.83240713402</v>
       </c>
-      <c r="P35" s="41">
+      <c r="P35" s="29">
         <v>11.323878680553101</v>
       </c>
-      <c r="Q35" s="41">
+      <c r="Q35" s="29">
         <v>8.8681469294123492</v>
       </c>
-      <c r="R35" s="41">
+      <c r="R35" s="29">
         <v>14.213890428250499</v>
       </c>
       <c r="S35">
@@ -6709,7 +6709,7 @@
       <c r="H36">
         <v>0.13953488372093001</v>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>13.953488372093</v>
       </c>
@@ -6731,13 +6731,13 @@
       <c r="O36">
         <v>8.0132737704877606</v>
       </c>
-      <c r="P36" s="41">
+      <c r="P36" s="29">
         <v>11.3474118772388</v>
       </c>
-      <c r="Q36" s="41">
+      <c r="Q36" s="29">
         <v>8.9253611430419006</v>
       </c>
-      <c r="R36" s="41">
+      <c r="R36" s="29">
         <v>14.695293804311399</v>
       </c>
       <c r="S36">
@@ -6787,7 +6787,7 @@
       <c r="H37">
         <v>9.2219020172910698E-2</v>
       </c>
-      <c r="I37" s="41">
+      <c r="I37" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>9.22190201729107</v>
       </c>
@@ -6809,13 +6809,13 @@
       <c r="O37">
         <v>12.0716643775549</v>
       </c>
-      <c r="P37" s="41">
+      <c r="P37" s="29">
         <v>11.4131997169369</v>
       </c>
-      <c r="Q37" s="41">
+      <c r="Q37" s="29">
         <v>8.9435998470631795</v>
       </c>
-      <c r="R37" s="41">
+      <c r="R37" s="29">
         <v>14.725658499400099</v>
       </c>
       <c r="S37">
@@ -6865,7 +6865,7 @@
       <c r="H38">
         <v>9.4202898550724598E-2</v>
       </c>
-      <c r="I38" s="41">
+      <c r="I38" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>9.4202898550724594</v>
       </c>
@@ -6887,13 +6887,13 @@
       <c r="O38">
         <v>10.8317551512213</v>
       </c>
-      <c r="P38" s="41">
+      <c r="P38" s="29">
         <v>11.6803035158093</v>
       </c>
-      <c r="Q38" s="41">
+      <c r="Q38" s="29">
         <v>8.5463519388035802</v>
       </c>
-      <c r="R38" s="41">
+      <c r="R38" s="29">
         <v>15.3313036866637</v>
       </c>
       <c r="S38">
@@ -6943,7 +6943,7 @@
       <c r="H39">
         <v>0.161764705882353</v>
       </c>
-      <c r="I39" s="41">
+      <c r="I39" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>16.176470588235301</v>
       </c>
@@ -6965,13 +6965,13 @@
       <c r="O39">
         <v>8.1519604339160594</v>
       </c>
-      <c r="P39" s="41">
+      <c r="P39" s="29">
         <v>11.705955414872401</v>
       </c>
-      <c r="Q39" s="41">
+      <c r="Q39" s="29">
         <v>8.9296128673371502</v>
       </c>
-      <c r="R39" s="41">
+      <c r="R39" s="29">
         <v>15.181831256997199</v>
       </c>
       <c r="S39">
@@ -7021,7 +7021,7 @@
       <c r="H40">
         <v>0.13736263736263701</v>
       </c>
-      <c r="I40" s="41">
+      <c r="I40" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>13.736263736263702</v>
       </c>
@@ -7043,13 +7043,13 @@
       <c r="O40">
         <v>9.2548925564024902</v>
       </c>
-      <c r="P40" s="41">
+      <c r="P40" s="29">
         <v>11.870323652762</v>
       </c>
-      <c r="Q40" s="41">
+      <c r="Q40" s="29">
         <v>8.8428157774297294</v>
       </c>
-      <c r="R40" s="41">
+      <c r="R40" s="29">
         <v>15.3483132012762</v>
       </c>
       <c r="S40">
@@ -7099,7 +7099,7 @@
       <c r="H41">
         <v>0.123214285714286</v>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>12.3214285714286</v>
       </c>
@@ -7121,13 +7121,13 @@
       <c r="O41">
         <v>10.3462412964324</v>
       </c>
-      <c r="P41" s="41">
+      <c r="P41" s="29">
         <v>12.1356363652057</v>
       </c>
-      <c r="Q41" s="41">
+      <c r="Q41" s="29">
         <v>9.6449508384105798</v>
       </c>
-      <c r="R41" s="41">
+      <c r="R41" s="29">
         <v>15.1862103152404</v>
       </c>
       <c r="S41">
@@ -7177,7 +7177,7 @@
       <c r="H42">
         <v>0.104166666666667</v>
       </c>
-      <c r="I42" s="41">
+      <c r="I42" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>10.4166666666667</v>
       </c>
@@ -7199,13 +7199,13 @@
       <c r="O42">
         <v>11.217879572130199</v>
       </c>
-      <c r="P42" s="41">
+      <c r="P42" s="29">
         <v>12.2244311637987</v>
       </c>
-      <c r="Q42" s="41">
+      <c r="Q42" s="29">
         <v>9.1709986234143095</v>
       </c>
-      <c r="R42" s="41">
+      <c r="R42" s="29">
         <v>16.077008824796302</v>
       </c>
       <c r="S42">
@@ -7255,7 +7255,7 @@
       <c r="H43">
         <v>0.11726384364820799</v>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>11.726384364820799</v>
       </c>
@@ -7277,13 +7277,13 @@
       <c r="O43">
         <v>11.7285146399204</v>
       </c>
-      <c r="P43" s="41">
+      <c r="P43" s="29">
         <v>12.609324482051401</v>
       </c>
-      <c r="Q43" s="41">
+      <c r="Q43" s="29">
         <v>9.7712624816219105</v>
       </c>
-      <c r="R43" s="41">
+      <c r="R43" s="29">
         <v>16.467604474133999</v>
       </c>
       <c r="S43">
@@ -7333,7 +7333,7 @@
       <c r="H44">
         <v>0.14285714285714299</v>
       </c>
-      <c r="I44" s="41">
+      <c r="I44" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>14.285714285714299</v>
       </c>
@@ -7355,13 +7355,13 @@
       <c r="O44">
         <v>10.163060293120401</v>
       </c>
-      <c r="P44" s="41">
+      <c r="P44" s="29">
         <v>12.9515292923583</v>
       </c>
-      <c r="Q44" s="41">
+      <c r="Q44" s="29">
         <v>10.0946530323594</v>
       </c>
-      <c r="R44" s="41">
+      <c r="R44" s="29">
         <v>16.320305851233201</v>
       </c>
       <c r="S44">
@@ -7411,7 +7411,7 @@
       <c r="H45">
         <v>0.141463414634146</v>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>14.146341463414599</v>
       </c>
@@ -7433,13 +7433,13 @@
       <c r="O45">
         <v>10.012551996605801</v>
       </c>
-      <c r="P45" s="41">
+      <c r="P45" s="29">
         <v>12.9926675952438</v>
       </c>
-      <c r="Q45" s="41">
+      <c r="Q45" s="29">
         <v>10.2399539162318</v>
       </c>
-      <c r="R45" s="41">
+      <c r="R45" s="29">
         <v>16.444225606987299</v>
       </c>
       <c r="S45">
@@ -7489,7 +7489,7 @@
       <c r="H46">
         <v>0.119791666666667</v>
       </c>
-      <c r="I46" s="41">
+      <c r="I46" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>11.9791666666667</v>
       </c>
@@ -7511,13 +7511,13 @@
       <c r="O46">
         <v>12.298849461073599</v>
       </c>
-      <c r="P46" s="41">
+      <c r="P46" s="29">
         <v>13.220614253604801</v>
       </c>
-      <c r="Q46" s="41">
+      <c r="Q46" s="29">
         <v>10.1170142876543</v>
       </c>
-      <c r="R46" s="41">
+      <c r="R46" s="29">
         <v>17.1875610621262</v>
       </c>
       <c r="S46">
@@ -7567,7 +7567,7 @@
       <c r="H47">
         <v>0.124444444444444</v>
       </c>
-      <c r="I47" s="41">
+      <c r="I47" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>12.4444444444444</v>
       </c>
@@ -7589,13 +7589,13 @@
       <c r="O47">
         <v>12.488270603755501</v>
       </c>
-      <c r="P47" s="41">
+      <c r="P47" s="29">
         <v>13.394133913234199</v>
       </c>
-      <c r="Q47" s="41">
+      <c r="Q47" s="29">
         <v>10.4456417551055</v>
       </c>
-      <c r="R47" s="41">
+      <c r="R47" s="29">
         <v>17.112476940255998</v>
       </c>
       <c r="S47">
@@ -7645,7 +7645,7 @@
       <c r="H48">
         <v>0.13157894736842099</v>
       </c>
-      <c r="I48" s="41">
+      <c r="I48" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>13.157894736842099</v>
       </c>
@@ -7667,13 +7667,13 @@
       <c r="O48">
         <v>12.431297018256201</v>
       </c>
-      <c r="P48" s="41">
+      <c r="P48" s="29">
         <v>13.6167224036297</v>
       </c>
-      <c r="Q48" s="41">
+      <c r="Q48" s="29">
         <v>10.826186246917</v>
       </c>
-      <c r="R48" s="41">
+      <c r="R48" s="29">
         <v>17.2551748952223</v>
       </c>
       <c r="S48">
@@ -7723,7 +7723,7 @@
       <c r="H49">
         <v>0.13362068965517199</v>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>13.362068965517199</v>
       </c>
@@ -7745,13 +7745,13 @@
       <c r="O49">
         <v>12.1803936680713</v>
       </c>
-      <c r="P49" s="41">
+      <c r="P49" s="29">
         <v>13.768378202492199</v>
       </c>
-      <c r="Q49" s="41">
+      <c r="Q49" s="29">
         <v>10.666055556281799</v>
       </c>
-      <c r="R49" s="41">
+      <c r="R49" s="29">
         <v>17.933071550538301</v>
       </c>
       <c r="S49">
@@ -7801,7 +7801,7 @@
       <c r="H50">
         <v>0.22222222222222199</v>
       </c>
-      <c r="I50" s="41">
+      <c r="I50" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>22.2222222222222</v>
       </c>
@@ -7823,13 +7823,13 @@
       <c r="O50">
         <v>10.7844926498872</v>
       </c>
-      <c r="P50" s="41">
+      <c r="P50" s="29">
         <v>14.169550787956601</v>
       </c>
-      <c r="Q50" s="41">
+      <c r="Q50" s="29">
         <v>10.553018155742199</v>
       </c>
-      <c r="R50" s="41">
+      <c r="R50" s="29">
         <v>18.864499007564699</v>
       </c>
       <c r="S50">
@@ -7879,7 +7879,7 @@
       <c r="H51">
         <v>0.13063063063063099</v>
       </c>
-      <c r="I51" s="41">
+      <c r="I51" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>13.063063063063099</v>
       </c>
@@ -7901,13 +7901,13 @@
       <c r="O51">
         <v>14.2800543747557</v>
       </c>
-      <c r="P51" s="41">
+      <c r="P51" s="29">
         <v>15.094662254443</v>
       </c>
-      <c r="Q51" s="41">
+      <c r="Q51" s="29">
         <v>11.7844215294941</v>
       </c>
-      <c r="R51" s="41">
+      <c r="R51" s="29">
         <v>19.1442457372954</v>
       </c>
       <c r="S51">
@@ -7957,7 +7957,7 @@
       <c r="H52">
         <v>0.126050420168067</v>
       </c>
-      <c r="I52" s="41">
+      <c r="I52" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>12.605042016806699</v>
       </c>
@@ -7979,13 +7979,13 @@
       <c r="O52">
         <v>14.0753417114275</v>
       </c>
-      <c r="P52" s="41">
+      <c r="P52" s="29">
         <v>15.128438451205099</v>
       </c>
-      <c r="Q52" s="41">
+      <c r="Q52" s="29">
         <v>11.1920416981913</v>
       </c>
-      <c r="R52" s="41">
+      <c r="R52" s="29">
         <v>19.763822973106102</v>
       </c>
       <c r="S52">
@@ -8035,7 +8035,7 @@
       <c r="H53">
         <v>0.15909090909090901</v>
       </c>
-      <c r="I53" s="41">
+      <c r="I53" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>15.909090909090901</v>
       </c>
@@ -8057,13 +8057,13 @@
       <c r="O53">
         <v>14.331901625566299</v>
       </c>
-      <c r="P53" s="41">
+      <c r="P53" s="29">
         <v>16.074415566126401</v>
       </c>
-      <c r="Q53" s="41">
+      <c r="Q53" s="29">
         <v>12.731544421852901</v>
       </c>
-      <c r="R53" s="41">
+      <c r="R53" s="29">
         <v>20.583358723324199</v>
       </c>
       <c r="S53">
@@ -8113,7 +8113,7 @@
       <c r="H54">
         <v>0.16289592760180999</v>
       </c>
-      <c r="I54" s="41">
+      <c r="I54" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>16.289592760180998</v>
       </c>
@@ -8135,13 +8135,13 @@
       <c r="O54">
         <v>13.946415820358901</v>
       </c>
-      <c r="P54" s="41">
+      <c r="P54" s="29">
         <v>16.130889483403401</v>
       </c>
-      <c r="Q54" s="41">
+      <c r="Q54" s="29">
         <v>12.5314592144064</v>
       </c>
-      <c r="R54" s="41">
+      <c r="R54" s="29">
         <v>21.0055398532871</v>
       </c>
       <c r="S54">
@@ -8191,7 +8191,7 @@
       <c r="H55">
         <v>0.159151193633952</v>
       </c>
-      <c r="I55" s="41">
+      <c r="I55" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>15.915119363395199</v>
       </c>
@@ -8213,13 +8213,13 @@
       <c r="O55">
         <v>15.5316993133744</v>
       </c>
-      <c r="P55" s="41">
+      <c r="P55" s="29">
         <v>16.493225286717902</v>
       </c>
-      <c r="Q55" s="41">
+      <c r="Q55" s="29">
         <v>13.224733746400601</v>
       </c>
-      <c r="R55" s="41">
+      <c r="R55" s="29">
         <v>20.409435566170998</v>
       </c>
       <c r="S55">
@@ -8269,7 +8269,7 @@
       <c r="H56">
         <v>0.171597633136095</v>
       </c>
-      <c r="I56" s="41">
+      <c r="I56" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>17.159763313609499</v>
       </c>
@@ -8291,13 +8291,13 @@
       <c r="O56">
         <v>13.800464773584901</v>
       </c>
-      <c r="P56" s="41">
+      <c r="P56" s="29">
         <v>16.546912047321101</v>
       </c>
-      <c r="Q56" s="41">
+      <c r="Q56" s="29">
         <v>13.273985132991299</v>
       </c>
-      <c r="R56" s="41">
+      <c r="R56" s="29">
         <v>20.831483415227101</v>
       </c>
       <c r="S56">
@@ -8347,7 +8347,7 @@
       <c r="H57">
         <v>0.16022099447513799</v>
       </c>
-      <c r="I57" s="41">
+      <c r="I57" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>16.022099447513799</v>
       </c>
@@ -8369,13 +8369,13 @@
       <c r="O57">
         <v>15.9943923572897</v>
       </c>
-      <c r="P57" s="41">
+      <c r="P57" s="29">
         <v>16.5767407829143</v>
       </c>
-      <c r="Q57" s="41">
+      <c r="Q57" s="29">
         <v>13.546634944253899</v>
       </c>
-      <c r="R57" s="41">
+      <c r="R57" s="29">
         <v>20.271922954726001</v>
       </c>
       <c r="S57">
@@ -8425,7 +8425,7 @@
       <c r="H58">
         <v>0.175595238095238</v>
       </c>
-      <c r="I58" s="41">
+      <c r="I58" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>17.5595238095238</v>
       </c>
@@ -8447,13 +8447,13 @@
       <c r="O58">
         <v>14.124947393953599</v>
       </c>
-      <c r="P58" s="41">
+      <c r="P58" s="29">
         <v>17.096770641010899</v>
       </c>
-      <c r="Q58" s="41">
+      <c r="Q58" s="29">
         <v>13.458108773313</v>
       </c>
-      <c r="R58" s="41">
+      <c r="R58" s="29">
         <v>21.229674815215901</v>
       </c>
       <c r="S58">
@@ -8503,7 +8503,7 @@
       <c r="H59">
         <v>0.17042606516290701</v>
       </c>
-      <c r="I59" s="41">
+      <c r="I59" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>17.0426065162907</v>
       </c>
@@ -8525,13 +8525,13 @@
       <c r="O59">
         <v>17.613419341870099</v>
       </c>
-      <c r="P59" s="41">
+      <c r="P59" s="29">
         <v>18.3103763802057</v>
       </c>
-      <c r="Q59" s="41">
+      <c r="Q59" s="29">
         <v>14.6477112373354</v>
       </c>
-      <c r="R59" s="41">
+      <c r="R59" s="29">
         <v>22.1995768096455</v>
       </c>
       <c r="S59">
@@ -8581,7 +8581,7 @@
       <c r="H60">
         <v>0.21052631578947401</v>
       </c>
-      <c r="I60" s="41">
+      <c r="I60" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>21.052631578947402</v>
       </c>
@@ -8603,13 +8603,13 @@
       <c r="O60">
         <v>14.4677898710055</v>
       </c>
-      <c r="P60" s="41">
+      <c r="P60" s="29">
         <v>18.439613146187</v>
       </c>
-      <c r="Q60" s="41">
+      <c r="Q60" s="29">
         <v>14.297825543126899</v>
       </c>
-      <c r="R60" s="41">
+      <c r="R60" s="29">
         <v>23.129522636805302</v>
       </c>
       <c r="S60">
@@ -8659,7 +8659,7 @@
       <c r="H61">
         <v>0.19230769230769201</v>
       </c>
-      <c r="I61" s="41">
+      <c r="I61" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>19.230769230769202</v>
       </c>
@@ -8681,13 +8681,13 @@
       <c r="O61">
         <v>16.427497411778202</v>
       </c>
-      <c r="P61" s="41">
+      <c r="P61" s="29">
         <v>18.909700314044201</v>
       </c>
-      <c r="Q61" s="41">
+      <c r="Q61" s="29">
         <v>14.7435874838985</v>
       </c>
-      <c r="R61" s="41">
+      <c r="R61" s="29">
         <v>23.838293336937301</v>
       </c>
       <c r="S61">
@@ -8737,7 +8737,7 @@
       <c r="H62">
         <v>0.241025641025641</v>
       </c>
-      <c r="I62" s="41">
+      <c r="I62" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>24.102564102564099</v>
       </c>
@@ -8759,13 +8759,13 @@
       <c r="O62">
         <v>13.8832451891791</v>
       </c>
-      <c r="P62" s="41">
+      <c r="P62" s="29">
         <v>19.4672498760733</v>
       </c>
-      <c r="Q62" s="41">
+      <c r="Q62" s="29">
         <v>15.5256438000266</v>
       </c>
-      <c r="R62" s="41">
+      <c r="R62" s="29">
         <v>24.411234545626101</v>
       </c>
       <c r="S62">
@@ -8815,7 +8815,7 @@
       <c r="H63">
         <v>0.191176470588235</v>
       </c>
-      <c r="I63" s="41">
+      <c r="I63" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>19.117647058823501</v>
       </c>
@@ -8837,13 +8837,13 @@
       <c r="O63">
         <v>17.940833850053298</v>
       </c>
-      <c r="P63" s="41">
+      <c r="P63" s="29">
         <v>19.5580926823807</v>
       </c>
-      <c r="Q63" s="41">
+      <c r="Q63" s="29">
         <v>16.2895498697095</v>
       </c>
-      <c r="R63" s="41">
+      <c r="R63" s="29">
         <v>23.317338027969502</v>
       </c>
       <c r="S63">
@@ -8893,7 +8893,7 @@
       <c r="H64">
         <v>0.22340425531914901</v>
       </c>
-      <c r="I64" s="41">
+      <c r="I64" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>22.340425531914899</v>
       </c>
@@ -8915,13 +8915,13 @@
       <c r="O64">
         <v>14.783504593347001</v>
       </c>
-      <c r="P64" s="41">
+      <c r="P64" s="29">
         <v>19.815934120902099</v>
       </c>
-      <c r="Q64" s="41">
+      <c r="Q64" s="29">
         <v>15.8350250611976</v>
       </c>
-      <c r="R64" s="41">
+      <c r="R64" s="29">
         <v>24.727135122000298</v>
       </c>
       <c r="S64">
@@ -8971,7 +8971,7 @@
       <c r="H65">
         <v>0.20535714285714299</v>
       </c>
-      <c r="I65" s="41">
+      <c r="I65" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>20.535714285714299</v>
       </c>
@@ -8993,13 +8993,13 @@
       <c r="O65">
         <v>18.173182661806599</v>
       </c>
-      <c r="P65" s="41">
+      <c r="P65" s="29">
         <v>20.510127072497198</v>
       </c>
-      <c r="Q65" s="41">
+      <c r="Q65" s="29">
         <v>16.847363359131499</v>
       </c>
-      <c r="R65" s="41">
+      <c r="R65" s="29">
         <v>24.945857435248701</v>
       </c>
       <c r="S65">
@@ -9049,7 +9049,7 @@
       <c r="H66">
         <v>0.21186440677966101</v>
       </c>
-      <c r="I66" s="41">
+      <c r="I66" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>21.1864406779661</v>
       </c>
@@ -9071,13 +9071,13 @@
       <c r="O66">
         <v>18.792446783260299</v>
       </c>
-      <c r="P66" s="41">
+      <c r="P66" s="29">
         <v>21.245155193705099</v>
       </c>
-      <c r="Q66" s="41">
+      <c r="Q66" s="29">
         <v>17.545827040103699</v>
       </c>
-      <c r="R66" s="41">
+      <c r="R66" s="29">
         <v>25.786444877101701</v>
       </c>
       <c r="S66">
@@ -9127,7 +9127,7 @@
       <c r="H67">
         <v>0.23404255319148901</v>
       </c>
-      <c r="I67" s="41">
+      <c r="I67" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>23.404255319148902</v>
       </c>
@@ -9149,13 +9149,13 @@
       <c r="O67">
         <v>18.2489956922097</v>
       </c>
-      <c r="P67" s="41">
+      <c r="P67" s="29">
         <v>22.5767208337056</v>
       </c>
-      <c r="Q67" s="41">
+      <c r="Q67" s="29">
         <v>18.477016401436</v>
       </c>
-      <c r="R67" s="41">
+      <c r="R67" s="29">
         <v>26.679445797071299</v>
       </c>
       <c r="S67">
@@ -9205,7 +9205,7 @@
       <c r="H68">
         <v>0.22292993630573199</v>
       </c>
-      <c r="I68" s="41">
+      <c r="I68" s="29">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>22.2929936305732</v>
       </c>
@@ -9227,13 +9227,13 @@
       <c r="O68">
         <v>20.855111198347998</v>
       </c>
-      <c r="P68" s="41">
+      <c r="P68" s="29">
         <v>22.786956226844801</v>
       </c>
-      <c r="Q68" s="41">
+      <c r="Q68" s="29">
         <v>18.391218011460499</v>
       </c>
-      <c r="R68" s="41">
+      <c r="R68" s="29">
         <v>27.7724052002572</v>
       </c>
       <c r="S68">
@@ -9283,7 +9283,7 @@
       <c r="H69" s="2">
         <v>0.22929936305732501</v>
       </c>
-      <c r="I69" s="42">
+      <c r="I69" s="30">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>22.9299363057325</v>
       </c>
@@ -9305,13 +9305,13 @@
       <c r="O69" s="2">
         <v>20.758025372540398</v>
       </c>
-      <c r="P69" s="42">
+      <c r="P69" s="30">
         <v>23.3837031842281</v>
       </c>
-      <c r="Q69" s="42">
+      <c r="Q69" s="30">
         <v>18.4252391722788</v>
       </c>
-      <c r="R69" s="42">
+      <c r="R69" s="30">
         <v>29.028276174437199</v>
       </c>
       <c r="S69" s="2">
@@ -9361,7 +9361,7 @@
       <c r="H70" s="2">
         <v>0.276422764227642</v>
       </c>
-      <c r="I70" s="42">
+      <c r="I70" s="30">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>27.642276422764201</v>
       </c>
@@ -9383,13 +9383,13 @@
       <c r="O70" s="2">
         <v>17.868963539910101</v>
       </c>
-      <c r="P70" s="42">
+      <c r="P70" s="30">
         <v>24.2255532699638</v>
       </c>
-      <c r="Q70" s="42">
+      <c r="Q70" s="30">
         <v>19.5494206474905</v>
       </c>
-      <c r="R70" s="42">
+      <c r="R70" s="30">
         <v>29.482716426416999</v>
       </c>
       <c r="S70" s="2">
@@ -9439,7 +9439,7 @@
       <c r="H71" s="2">
         <v>0.27710843373493999</v>
       </c>
-      <c r="I71" s="42">
+      <c r="I71" s="30">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>27.710843373493997</v>
       </c>
@@ -9461,13 +9461,13 @@
       <c r="O71" s="2">
         <v>21.1750307373627</v>
       </c>
-      <c r="P71" s="42">
+      <c r="P71" s="30">
         <v>26.076964328873601</v>
       </c>
-      <c r="Q71" s="42">
+      <c r="Q71" s="30">
         <v>21.297945732926902</v>
       </c>
-      <c r="R71" s="42">
+      <c r="R71" s="30">
         <v>31.7484952096226</v>
       </c>
       <c r="S71" s="2">
@@ -9517,7 +9517,7 @@
       <c r="H72" s="2">
         <v>0.321937321937322</v>
       </c>
-      <c r="I72" s="42">
+      <c r="I72" s="30">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>32.193732193732203</v>
       </c>
@@ -9539,13 +9539,13 @@
       <c r="O72" s="2">
         <v>25.911587849766502</v>
       </c>
-      <c r="P72" s="42">
+      <c r="P72" s="30">
         <v>31.262096754752399</v>
       </c>
-      <c r="Q72" s="42">
+      <c r="Q72" s="30">
         <v>26.298132537779601</v>
       </c>
-      <c r="R72" s="42">
+      <c r="R72" s="30">
         <v>36.095992590823002</v>
       </c>
       <c r="S72" s="2">
@@ -9595,7 +9595,7 @@
       <c r="H73" s="2">
         <v>0.32405566600397601</v>
       </c>
-      <c r="I73" s="42">
+      <c r="I73" s="30">
         <f>Table3[[#This Row],[sedentarismo2]]*100</f>
         <v>32.405566600397599</v>
       </c>
@@ -9617,13 +9617,13 @@
       <c r="O73" s="2">
         <v>26.426260159443</v>
       </c>
-      <c r="P73" s="42">
+      <c r="P73" s="30">
         <v>31.716860302513499</v>
       </c>
-      <c r="Q73" s="42">
+      <c r="Q73" s="30">
         <v>27.311141441408498</v>
       </c>
-      <c r="R73" s="42">
+      <c r="R73" s="30">
         <v>36.565044986827303</v>
       </c>
       <c r="S73" s="2">
@@ -9660,7 +9660,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
     <col min="2" max="2" width="9.21875" customWidth="1"/>
@@ -12613,7 +12613,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AEAEF5-EBDB-4210-BAA2-48E8D8062F6B}">
   <dimension ref="A1:AA73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
     <col min="2" max="2" width="9.21875" customWidth="1"/>
@@ -12622,18 +12622,18 @@
     <col min="6" max="6" width="9.21875" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="16" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="13.77734375" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="9.88671875" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" customWidth="1"/>
     <col min="21" max="21" width="11.109375" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
     <col min="23" max="23" width="9.21875" customWidth="1"/>

--- a/Tables/MAIHDA Tables_10-03-26.xlsx
+++ b/Tables/MAIHDA Tables_10-03-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38b97e870d12de33/Documents/UAH/PhD Documents/INEdatos/Analysis/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="11_F25DC773A252ABDACC10487F095D4F545ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35454E1A-84C0-4B90-8C44-209C04FD82F7}"/>
+  <xr:revisionPtr revIDLastSave="716" documentId="11_F25DC773A252ABDACC10487F095D4F545ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8359978C-3BC0-4D1B-A411-146E8D04A675}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="Figure 2 Predicted Probability" sheetId="3" r:id="rId4"/>
     <sheet name="Figure 3 Residual Simulation" sheetId="1" r:id="rId5"/>
     <sheet name="Figure 3 Residual no Simulation" sheetId="2" r:id="rId6"/>
+    <sheet name="STATA" sheetId="7" r:id="rId7"/>
+    <sheet name="Formulas" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="173">
   <si>
     <t>stratum</t>
   </si>
@@ -731,6 +733,21 @@
   <si>
     <t>sedentarismo3</t>
   </si>
+  <si>
+    <t>m1_diff_lo</t>
+  </si>
+  <si>
+    <t>m1_diff_hi</t>
+  </si>
+  <si>
+    <t>m1_diff</t>
+  </si>
+  <si>
+    <t>m1_diff_rank</t>
+  </si>
+  <si>
+    <t>edad</t>
+  </si>
 </sst>
 </file>
 
@@ -830,7 +847,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,6 +863,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,7 +921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -983,6 +1006,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -992,24 +1033,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1428,13 +1453,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30493F8C-7541-4087-8756-547165D1DA7B}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>47</v>
       </c>
@@ -1443,7 +1468,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
         <v>48</v>
       </c>
@@ -1455,7 +1480,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>49</v>
       </c>
@@ -1469,7 +1494,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>50</v>
       </c>
@@ -1481,7 +1506,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>51</v>
       </c>
@@ -1495,7 +1520,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>53</v>
       </c>
@@ -1509,13 +1534,13 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
@@ -1523,7 +1548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
@@ -1537,7 +1562,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>60</v>
       </c>
@@ -1559,7 +1584,7 @@
         <v>1.3888888888888888E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -1579,7 +1604,7 @@
         <v>9.7222222222222224E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>63</v>
       </c>
@@ -1601,7 +1626,7 @@
         <v>0.15277777777777779</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>65</v>
       </c>
@@ -1623,7 +1648,7 @@
         <v>0.18055555555555555</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>67</v>
       </c>
@@ -1645,7 +1670,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>69</v>
       </c>
@@ -1665,7 +1690,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>70</v>
       </c>
@@ -1687,7 +1712,7 @@
         <v>0.4861111111111111</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>72</v>
       </c>
@@ -1709,7 +1734,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>74</v>
       </c>
@@ -1729,7 +1754,7 @@
         <v>0.72222222222222221</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
@@ -1751,7 +1776,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>77</v>
       </c>
@@ -1773,7 +1798,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>79</v>
       </c>
@@ -1793,7 +1818,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>80</v>
       </c>
@@ -1815,7 +1840,7 @@
         <v>0.93055555555555558</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>82</v>
       </c>
@@ -1837,7 +1862,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
         <v>85</v>
       </c>
@@ -1857,7 +1882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E31" t="s">
         <v>149</v>
       </c>
@@ -1875,26 +1900,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DC0C2D-CA39-42D0-AAFA-943778B10C90}">
   <dimension ref="A1:E67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-    </row>
-    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+    </row>
+    <row r="3" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>87</v>
       </c>
@@ -1908,7 +1933,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>91</v>
       </c>
@@ -1922,55 +1947,55 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-    </row>
-    <row r="6" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+    </row>
+    <row r="6" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="37">
         <v>3.29</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+    </row>
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="37">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="37">
         <v>0.08</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-    </row>
-    <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="34">
         <v>72</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-    </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>96</v>
       </c>
@@ -1980,17 +2005,17 @@
       <c r="C10" s="39"/>
       <c r="D10" s="39"/>
     </row>
-    <row r="11" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>98</v>
       </c>
@@ -2000,34 +2025,34 @@
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="20"/>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-    </row>
-    <row r="19" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+    </row>
+    <row r="19" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>87</v>
       </c>
@@ -2041,7 +2066,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>91</v>
       </c>
@@ -2055,7 +2080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>106</v>
       </c>
@@ -2069,7 +2094,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>108</v>
       </c>
@@ -2083,7 +2108,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>110</v>
       </c>
@@ -2097,7 +2122,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>112</v>
       </c>
@@ -2111,7 +2136,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>114</v>
       </c>
@@ -2125,7 +2150,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>116</v>
       </c>
@@ -2139,7 +2164,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>118</v>
       </c>
@@ -2153,79 +2178,79 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="37" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-    </row>
-    <row r="29" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="40">
         <v>3.29</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
       <c r="E29" s="22"/>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="40">
         <v>0.03</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="22"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="40">
         <v>0.01</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
       <c r="E31" s="22"/>
     </row>
-    <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="41">
         <v>72</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="42">
         <v>19503</v>
       </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-    </row>
-    <row r="34" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+    </row>
+    <row r="34" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>98</v>
       </c>
@@ -2237,18 +2262,18 @@
         <v>0.79442480000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
         <v>127</v>
       </c>
       <c r="C37" s="8"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>131</v>
       </c>
@@ -2257,7 +2282,7 @@
       </c>
       <c r="C39" s="8"/>
     </row>
-    <row r="40" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>87</v>
       </c>
@@ -2274,7 +2299,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>91</v>
       </c>
@@ -2291,7 +2316,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>106</v>
       </c>
@@ -2304,7 +2329,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>108</v>
       </c>
@@ -2317,7 +2342,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>110</v>
       </c>
@@ -2330,7 +2355,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>112</v>
       </c>
@@ -2343,7 +2368,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>114</v>
       </c>
@@ -2356,7 +2381,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>116</v>
       </c>
@@ -2369,7 +2394,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>118</v>
       </c>
@@ -2382,81 +2407,81 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="37" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-    </row>
-    <row r="51" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="34">
+      <c r="B51" s="40">
         <v>3.29</v>
       </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34">
+      <c r="C51" s="40"/>
+      <c r="D51" s="40">
         <v>3.29</v>
       </c>
-      <c r="E51" s="34"/>
-    </row>
-    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E51" s="40"/>
+    </row>
+    <row r="52" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34" t="s">
+      <c r="C52" s="40"/>
+      <c r="D52" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="34"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E52" s="40"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B53" s="34">
+      <c r="B53" s="40">
         <v>0.08</v>
       </c>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34">
+      <c r="C53" s="40"/>
+      <c r="D53" s="40">
         <v>0.01</v>
       </c>
-      <c r="E53" s="34"/>
-    </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E53" s="40"/>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35" t="s">
+      <c r="C54" s="41"/>
+      <c r="D54" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="E54" s="35"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E54" s="41"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B55" s="36">
+      <c r="B55" s="42">
         <v>19500</v>
       </c>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36">
+      <c r="C55" s="42"/>
+      <c r="D55" s="42">
         <v>19500</v>
       </c>
-      <c r="E55" s="36"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E55" s="42"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>134</v>
       </c>
@@ -2464,7 +2489,7 @@
         <v>7.7580510000000005E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
         <v>135</v>
       </c>
@@ -2472,7 +2497,7 @@
         <v>7.9442479999999992E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="27" t="s">
         <v>136</v>
       </c>
@@ -2480,10 +2505,10 @@
         <v>90.47878</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="27"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="27" t="s">
         <v>137</v>
       </c>
@@ -2491,7 +2516,7 @@
         <v>0.64979770000000003</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
         <v>138</v>
       </c>
@@ -2499,7 +2524,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
         <v>139</v>
       </c>
@@ -2507,7 +2532,7 @@
         <v>0.64516010000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
         <v>140</v>
       </c>
@@ -2515,29 +2540,34 @@
         <v>0.63441369999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>143</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
@@ -2549,17 +2579,12 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2568,14 +2593,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE5C60F-1F9A-44BA-B029-B52BD23DE95C}">
   <dimension ref="A1:C74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
         <v>129</v>
       </c>
@@ -2583,7 +2608,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>11111</v>
       </c>
@@ -2594,7 +2619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>11112</v>
       </c>
@@ -2605,7 +2630,7 @@
         <v>7.9847908745247196</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>11121</v>
       </c>
@@ -2616,7 +2641,7 @@
         <v>2.64900662251656</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11122</v>
       </c>
@@ -2627,7 +2652,7 @@
         <v>10.1123595505618</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>11131</v>
       </c>
@@ -2638,7 +2663,7 @@
         <v>8.2089552238806007</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>11132</v>
       </c>
@@ -2649,7 +2674,7 @@
         <v>8.6876155268022206</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11211</v>
       </c>
@@ -2660,7 +2685,7 @@
         <v>9.5238095238095202</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>11212</v>
       </c>
@@ -2671,7 +2696,7 @@
         <v>8.5714285714285694</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11221</v>
       </c>
@@ -2682,7 +2707,7 @@
         <v>8.1081081081081106</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11222</v>
       </c>
@@ -2693,7 +2718,7 @@
         <v>14.146341463414601</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11231</v>
       </c>
@@ -2704,7 +2729,7 @@
         <v>13.953488372093</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11232</v>
       </c>
@@ -2715,7 +2740,7 @@
         <v>12.3214285714286</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12111</v>
       </c>
@@ -2726,7 +2751,7 @@
         <v>4.9382716049382704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12112</v>
       </c>
@@ -2737,7 +2762,7 @@
         <v>5.7591623036649198</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>12121</v>
       </c>
@@ -2748,7 +2773,7 @@
         <v>8.0291970802919703</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>12122</v>
       </c>
@@ -2759,7 +2784,7 @@
         <v>7.8260869565217401</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>12131</v>
       </c>
@@ -2770,7 +2795,7 @@
         <v>6.3745019920318704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>12132</v>
       </c>
@@ -2781,7 +2806,7 @@
         <v>8.0971659919028305</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>12211</v>
       </c>
@@ -2792,7 +2817,7 @@
         <v>8.84353741496599</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>12212</v>
       </c>
@@ -2803,7 +2828,7 @@
         <v>10.4234527687296</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>12221</v>
       </c>
@@ -2814,7 +2839,7 @@
         <v>16.176470588235301</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>12222</v>
       </c>
@@ -2825,7 +2850,7 @@
         <v>7.4175824175824197</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12231</v>
       </c>
@@ -2836,7 +2861,7 @@
         <v>9.79020979020979</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>12232</v>
       </c>
@@ -2847,7 +2872,7 @@
         <v>10.5675146771037</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>13111</v>
       </c>
@@ -2858,7 +2883,7 @@
         <v>3.2258064516128999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13112</v>
       </c>
@@ -2869,7 +2894,7 @@
         <v>10.4477611940298</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13121</v>
       </c>
@@ -2880,7 +2905,7 @@
         <v>11.214953271028</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>13122</v>
       </c>
@@ -2891,7 +2916,7 @@
         <v>14.285714285714301</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>13131</v>
       </c>
@@ -2902,7 +2927,7 @@
         <v>6.6666666666666696</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>13132</v>
       </c>
@@ -2913,7 +2938,7 @@
         <v>10.4627766599598</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>13211</v>
       </c>
@@ -2924,7 +2949,7 @@
         <v>6.3380281690140796</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>13212</v>
       </c>
@@ -2935,7 +2960,7 @@
         <v>9.22190201729107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>13221</v>
       </c>
@@ -2946,7 +2971,7 @@
         <v>11.9791666666667</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>13222</v>
       </c>
@@ -2957,7 +2982,7 @@
         <v>15.915119363395201</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>13231</v>
       </c>
@@ -2968,7 +2993,7 @@
         <v>12.4444444444444</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>13232</v>
       </c>
@@ -2979,7 +3004,7 @@
         <v>16.022099447513799</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>21111</v>
       </c>
@@ -2990,7 +3015,7 @@
         <v>4.4776119402985097</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>21112</v>
       </c>
@@ -3001,7 +3026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>21121</v>
       </c>
@@ -3012,7 +3037,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>21122</v>
       </c>
@@ -3023,7 +3048,7 @@
         <v>11.726384364820801</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>21131</v>
       </c>
@@ -3034,7 +3059,7 @@
         <v>9.8113207547169807</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>21132</v>
       </c>
@@ -3045,7 +3070,7 @@
         <v>9.5330739299610894</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>21211</v>
       </c>
@@ -3056,7 +3081,7 @@
         <v>9.4202898550724594</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>21212</v>
       </c>
@@ -3067,7 +3092,7 @@
         <v>17.159763313609499</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>21221</v>
       </c>
@@ -3078,7 +3103,7 @@
         <v>16.289592760181002</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>21222</v>
       </c>
@@ -3089,7 +3114,7 @@
         <v>17.0426065162907</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>21231</v>
       </c>
@@ -3100,7 +3125,7 @@
         <v>17.5595238095238</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>21232</v>
       </c>
@@ -3111,7 +3136,7 @@
         <v>19.117647058823501</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>22111</v>
       </c>
@@ -3122,7 +3147,7 @@
         <v>2.5974025974026</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>22112</v>
       </c>
@@ -3133,7 +3158,7 @@
         <v>13.7362637362637</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>22121</v>
       </c>
@@ -3144,7 +3169,7 @@
         <v>7.03125</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>22122</v>
       </c>
@@ -3155,7 +3180,7 @@
         <v>13.362068965517199</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>22131</v>
       </c>
@@ -3166,7 +3191,7 @@
         <v>10.2459016393443</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>22132</v>
       </c>
@@ -3177,7 +3202,7 @@
         <v>13.157894736842101</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>22211</v>
       </c>
@@ -3188,7 +3213,7 @@
         <v>10.4166666666667</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>22212</v>
       </c>
@@ -3199,7 +3224,7 @@
         <v>15.909090909090899</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>22221</v>
       </c>
@@ -3210,7 +3235,7 @@
         <v>21.052631578947398</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>22222</v>
       </c>
@@ -3221,7 +3246,7 @@
         <v>20.535714285714299</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>22231</v>
       </c>
@@ -3232,7 +3257,7 @@
         <v>22.340425531914899</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>22232</v>
       </c>
@@ -3243,7 +3268,7 @@
         <v>21.1864406779661</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>23111</v>
       </c>
@@ -3254,7 +3279,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>23112</v>
       </c>
@@ -3265,7 +3290,7 @@
         <v>24.102564102564099</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>23121</v>
       </c>
@@ -3276,7 +3301,7 @@
         <v>12.605042016806699</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>23122</v>
       </c>
@@ -3287,7 +3312,7 @@
         <v>27.642276422764201</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>23131</v>
       </c>
@@ -3298,7 +3323,7 @@
         <v>13.063063063063099</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>23132</v>
       </c>
@@ -3309,7 +3334,7 @@
         <v>23.404255319148898</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>23211</v>
       </c>
@@ -3320,7 +3345,7 @@
         <v>19.230769230769202</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>23212</v>
       </c>
@@ -3331,7 +3356,7 @@
         <v>22.2929936305732</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>23221</v>
       </c>
@@ -3342,7 +3367,7 @@
         <v>22.9299363057325</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>23222</v>
       </c>
@@ -3353,7 +3378,7 @@
         <v>32.193732193732203</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>23231</v>
       </c>
@@ -3364,7 +3389,7 @@
         <v>27.710843373494001</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>23232</v>
       </c>
@@ -3383,33 +3408,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B49F686-15BB-461D-9535-4954B854B5B7}">
   <dimension ref="A1:AP73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="8" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9.28515625" customWidth="1"/>
+    <col min="8" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="13.88671875" customWidth="1"/>
-    <col min="16" max="16" width="13.77734375" customWidth="1"/>
-    <col min="17" max="17" width="13.44140625" customWidth="1"/>
-    <col min="18" max="18" width="12.5546875" customWidth="1"/>
-    <col min="20" max="20" width="13.33203125" customWidth="1"/>
-    <col min="21" max="21" width="9.88671875" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="10.28515625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="0" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="9" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="9.21875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="9.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3489,7 +3513,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>11111</v>
       </c>
@@ -3612,7 +3636,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>12111</v>
       </c>
@@ -3735,7 +3759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>11121</v>
       </c>
@@ -3858,7 +3882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>12112</v>
       </c>
@@ -3981,7 +4005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>12131</v>
       </c>
@@ -4104,7 +4128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12121</v>
       </c>
@@ -4227,7 +4251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>11112</v>
       </c>
@@ -4305,7 +4329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11131</v>
       </c>
@@ -4386,7 +4410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>13111</v>
       </c>
@@ -4509,7 +4533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11211</v>
       </c>
@@ -4632,7 +4656,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12211</v>
       </c>
@@ -4755,7 +4779,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>22111</v>
       </c>
@@ -4878,7 +4902,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>21111</v>
       </c>
@@ -5001,7 +5025,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12122</v>
       </c>
@@ -5124,7 +5148,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12132</v>
       </c>
@@ -5202,7 +5226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>11132</v>
       </c>
@@ -5280,7 +5304,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>11122</v>
       </c>
@@ -5358,7 +5382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>13131</v>
       </c>
@@ -5436,7 +5460,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>11221</v>
       </c>
@@ -5514,7 +5538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>11212</v>
       </c>
@@ -5592,7 +5616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>13112</v>
       </c>
@@ -5670,7 +5694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21121</v>
       </c>
@@ -5748,7 +5772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>13121</v>
       </c>
@@ -5826,7 +5850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>13211</v>
       </c>
@@ -5904,7 +5928,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>12231</v>
       </c>
@@ -5982,7 +6006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>12222</v>
       </c>
@@ -6060,7 +6084,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12212</v>
       </c>
@@ -6138,7 +6162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>22121</v>
       </c>
@@ -6216,7 +6240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>21112</v>
       </c>
@@ -6294,7 +6318,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>21131</v>
       </c>
@@ -6372,7 +6396,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>22131</v>
       </c>
@@ -6450,7 +6474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>13132</v>
       </c>
@@ -6528,7 +6552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>21132</v>
       </c>
@@ -6606,7 +6630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>12232</v>
       </c>
@@ -6684,7 +6708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11231</v>
       </c>
@@ -6762,7 +6786,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>13212</v>
       </c>
@@ -6840,7 +6864,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>21211</v>
       </c>
@@ -6918,7 +6942,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>12221</v>
       </c>
@@ -6996,7 +7020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>22112</v>
       </c>
@@ -7074,7 +7098,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>11232</v>
       </c>
@@ -7152,7 +7176,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>22211</v>
       </c>
@@ -7230,7 +7254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>21122</v>
       </c>
@@ -7308,7 +7332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>13122</v>
       </c>
@@ -7386,7 +7410,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>11222</v>
       </c>
@@ -7464,7 +7488,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>13221</v>
       </c>
@@ -7542,7 +7566,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>13231</v>
       </c>
@@ -7620,7 +7644,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>22132</v>
       </c>
@@ -7698,7 +7722,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>22122</v>
       </c>
@@ -7776,7 +7800,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>23111</v>
       </c>
@@ -7854,7 +7878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>23131</v>
       </c>
@@ -7932,7 +7956,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>23121</v>
       </c>
@@ -8010,7 +8034,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>22212</v>
       </c>
@@ -8088,7 +8112,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>21221</v>
       </c>
@@ -8166,7 +8190,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>13222</v>
       </c>
@@ -8244,7 +8268,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>21212</v>
       </c>
@@ -8322,7 +8346,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>13232</v>
       </c>
@@ -8400,7 +8424,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>21231</v>
       </c>
@@ -8478,7 +8502,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>21222</v>
       </c>
@@ -8556,7 +8580,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>22221</v>
       </c>
@@ -8634,7 +8658,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>23211</v>
       </c>
@@ -8712,7 +8736,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>23112</v>
       </c>
@@ -8790,7 +8814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>21232</v>
       </c>
@@ -8868,7 +8892,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>22231</v>
       </c>
@@ -8946,7 +8970,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>22222</v>
       </c>
@@ -9024,7 +9048,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>22232</v>
       </c>
@@ -9102,7 +9126,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>23132</v>
       </c>
@@ -9180,7 +9204,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>23212</v>
       </c>
@@ -9258,7 +9282,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>23221</v>
       </c>
@@ -9336,7 +9360,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>23122</v>
       </c>
@@ -9414,7 +9438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>23231</v>
       </c>
@@ -9492,7 +9516,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>23222</v>
       </c>
@@ -9570,7 +9594,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>23232</v>
       </c>
@@ -9660,25 +9684,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9719,7 +9742,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>21132</v>
       </c>
@@ -9793,7 +9816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>13212</v>
       </c>
@@ -9831,7 +9854,7 @@
         <v>-5.0512369386663201</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>12222</v>
       </c>
@@ -9872,7 +9895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>21222</v>
       </c>
@@ -9946,7 +9969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>23131</v>
       </c>
@@ -10020,7 +10043,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>13232</v>
       </c>
@@ -10094,7 +10117,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>13222</v>
       </c>
@@ -10132,7 +10155,7 @@
         <v>-4.6476595199868598</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>13211</v>
       </c>
@@ -10170,7 +10193,7 @@
         <v>-3.9025249214097602</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>22121</v>
       </c>
@@ -10208,7 +10231,7 @@
         <v>-3.92688380923083</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>21232</v>
       </c>
@@ -10246,7 +10269,7 @@
         <v>-4.5786556465027397</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>23121</v>
       </c>
@@ -10284,7 +10307,7 @@
         <v>-5.0486028505435003</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12232</v>
       </c>
@@ -10322,7 +10345,7 @@
         <v>-3.7626594561844602</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>21121</v>
       </c>
@@ -10360,7 +10383,7 @@
         <v>-3.8339370451715098</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13221</v>
       </c>
@@ -10398,7 +10421,7 @@
         <v>-4.1484203266210402</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>21122</v>
       </c>
@@ -10436,7 +10459,7 @@
         <v>-3.9249540148773598</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>23212</v>
       </c>
@@ -10474,7 +10497,7 @@
         <v>-5.4189157591194599</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>13131</v>
       </c>
@@ -10512,7 +10535,7 @@
         <v>-3.0220073285713198</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>13132</v>
       </c>
@@ -10550,7 +10573,7 @@
         <v>-3.5149071434541601</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>22132</v>
       </c>
@@ -10588,7 +10611,7 @@
         <v>-3.9382400654828502</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>22111</v>
       </c>
@@ -10626,7 +10649,7 @@
         <v>-3.1790992396814199</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22211</v>
       </c>
@@ -10664,7 +10687,7 @@
         <v>-4.0056235657839201</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21211</v>
       </c>
@@ -10702,7 +10725,7 @@
         <v>-4.1180938363045403</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>13231</v>
       </c>
@@ -10740,7 +10763,7 @@
         <v>-3.9757111610017</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>11121</v>
       </c>
@@ -10778,7 +10801,7 @@
         <v>-2.2648540532456001</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23221</v>
       </c>
@@ -10816,7 +10839,7 @@
         <v>-5.4525290975134304</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>13111</v>
       </c>
@@ -10854,7 +10877,7 @@
         <v>-2.5773187202934702</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>22222</v>
       </c>
@@ -10892,7 +10915,7 @@
         <v>-4.7131289968048202</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>22122</v>
       </c>
@@ -10930,7 +10953,7 @@
         <v>-3.8417452024150802</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>21131</v>
       </c>
@@ -10968,7 +10991,7 @@
         <v>-3.2128844093038502</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>11221</v>
       </c>
@@ -11006,7 +11029,7 @@
         <v>-2.9556777062128501</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>22131</v>
       </c>
@@ -11044,7 +11067,7 @@
         <v>-3.2631662991040602</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>21111</v>
       </c>
@@ -11082,7 +11105,7 @@
         <v>-3.0174660212720599</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>22212</v>
       </c>
@@ -11120,7 +11143,7 @@
         <v>-3.9019992649600499</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>12112</v>
       </c>
@@ -11158,7 +11181,7 @@
         <v>-1.7501903097047999</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11212</v>
       </c>
@@ -11196,7 +11219,7 @@
         <v>-2.4692907416624399</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>12132</v>
       </c>
@@ -11234,7 +11257,7 @@
         <v>-2.0562118742617699</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>11111</v>
       </c>
@@ -11272,7 +11295,7 @@
         <v>-1.44868079581926</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>22232</v>
       </c>
@@ -11310,7 +11333,7 @@
         <v>-3.8743453888087598</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>12111</v>
       </c>
@@ -11348,7 +11371,7 @@
         <v>-1.6719628655532199</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>12122</v>
       </c>
@@ -11386,7 +11409,7 @@
         <v>-2.5115327708917601</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>21112</v>
       </c>
@@ -11424,7 +11447,7 @@
         <v>-3.0351075184864502</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>12131</v>
       </c>
@@ -11462,7 +11485,7 @@
         <v>-1.8279351505717101</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>21221</v>
       </c>
@@ -11500,7 +11523,7 @@
         <v>-3.6596990640676301</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>12231</v>
       </c>
@@ -11538,7 +11561,7 @@
         <v>-2.6457400380041598</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>23211</v>
       </c>
@@ -11576,7 +11599,7 @@
         <v>-4.4282626480564797</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>12211</v>
       </c>
@@ -11614,7 +11637,7 @@
         <v>-1.9968699710692699</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>11232</v>
       </c>
@@ -11652,7 +11675,7 @@
         <v>-2.3021509879442199</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12121</v>
       </c>
@@ -11690,7 +11713,7 @@
         <v>-1.6520621091027901</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>13121</v>
       </c>
@@ -11728,7 +11751,7 @@
         <v>-2.4388341530458</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>12212</v>
       </c>
@@ -11766,7 +11789,7 @@
         <v>-2.0736806537200998</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>11132</v>
       </c>
@@ -11804,7 +11827,7 @@
         <v>-1.4574389614022101</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>13112</v>
       </c>
@@ -11842,7 +11865,7 @@
         <v>-2.25907000477121</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>11112</v>
       </c>
@@ -11880,7 +11903,7 @@
         <v>-1.4226068547153199</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>11211</v>
       </c>
@@ -11918,7 +11941,7 @@
         <v>-1.7370220591458301</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>21212</v>
       </c>
@@ -11956,7 +11979,7 @@
         <v>-3.2596284222516001</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>11131</v>
       </c>
@@ -11994,7 +12017,7 @@
         <v>-1.12794855917807</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>21231</v>
       </c>
@@ -12032,7 +12055,7 @@
         <v>-2.95848578963514</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>22112</v>
       </c>
@@ -12070,7 +12093,7 @@
         <v>-2.2894551138572101</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>11122</v>
       </c>
@@ -12108,7 +12131,7 @@
         <v>-1.30039988468137</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>13122</v>
       </c>
@@ -12146,7 +12169,7 @@
         <v>-1.8116411219558</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>11222</v>
       </c>
@@ -12184,7 +12207,7 @@
         <v>-1.34560430118315</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>23111</v>
       </c>
@@ -12222,7 +12245,7 @@
         <v>-2.3965417221963001</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>23232</v>
       </c>
@@ -12260,7 +12283,7 @@
         <v>-2.8112818284160399</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>22221</v>
       </c>
@@ -12298,7 +12321,7 @@
         <v>-2.6079209048146401</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>23132</v>
       </c>
@@ -12336,7 +12359,7 @@
         <v>-2.1608139978003398</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>23231</v>
       </c>
@@ -12374,7 +12397,7 @@
         <v>-3.0729563348651299</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>23222</v>
       </c>
@@ -12412,7 +12435,7 @@
         <v>-3.3911397018825999</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>11231</v>
       </c>
@@ -12450,7 +12473,7 @@
         <v>-0.738538394167229</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>12221</v>
       </c>
@@ -12488,7 +12511,7 @@
         <v>-0.64271481996711799</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>22231</v>
       </c>
@@ -12526,7 +12549,7 @@
         <v>-1.11294900995379</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>23112</v>
       </c>
@@ -12564,7 +12587,7 @@
         <v>-0.55981750209351999</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>23122</v>
       </c>
@@ -12613,33 +12636,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AEAEF5-EBDB-4210-BAA2-48E8D8062F6B}">
   <dimension ref="A1:AA73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" customWidth="1"/>
-    <col min="14" max="14" width="13.77734375" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" customWidth="1"/>
-    <col min="18" max="18" width="9.88671875" customWidth="1"/>
-    <col min="19" max="19" width="10.33203125" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" customWidth="1"/>
-    <col min="21" max="21" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
-    <col min="23" max="23" width="9.21875" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12716,7 +12738,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>13212</v>
       </c>
@@ -12790,7 +12812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>21132</v>
       </c>
@@ -12864,7 +12886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>12222</v>
       </c>
@@ -12938,7 +12960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>21222</v>
       </c>
@@ -13012,7 +13034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>13232</v>
       </c>
@@ -13086,7 +13108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>23131</v>
       </c>
@@ -13160,7 +13182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>13211</v>
       </c>
@@ -13234,7 +13256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>13222</v>
       </c>
@@ -13308,7 +13330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>23121</v>
       </c>
@@ -13382,7 +13404,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>12232</v>
       </c>
@@ -13456,7 +13478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>21121</v>
       </c>
@@ -13530,7 +13552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13131</v>
       </c>
@@ -13604,7 +13626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13231</v>
       </c>
@@ -13678,7 +13700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>22121</v>
       </c>
@@ -13752,7 +13774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13221</v>
       </c>
@@ -13826,7 +13848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13132</v>
       </c>
@@ -13900,7 +13922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>21122</v>
       </c>
@@ -13974,7 +13996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>22111</v>
       </c>
@@ -14048,7 +14070,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>22211</v>
       </c>
@@ -14122,7 +14144,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21232</v>
       </c>
@@ -14196,7 +14218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21211</v>
       </c>
@@ -14270,7 +14292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23212</v>
       </c>
@@ -14344,7 +14366,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22132</v>
       </c>
@@ -14418,7 +14440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>11121</v>
       </c>
@@ -14492,7 +14514,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23221</v>
       </c>
@@ -14566,7 +14588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>22212</v>
       </c>
@@ -14640,7 +14662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>21111</v>
       </c>
@@ -14714,7 +14736,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>22131</v>
       </c>
@@ -14788,7 +14810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>22222</v>
       </c>
@@ -14862,7 +14884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>13111</v>
       </c>
@@ -14936,7 +14958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>11221</v>
       </c>
@@ -15010,7 +15032,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>22122</v>
       </c>
@@ -15084,7 +15106,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>21131</v>
       </c>
@@ -15158,7 +15180,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>21112</v>
       </c>
@@ -15232,7 +15254,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11212</v>
       </c>
@@ -15306,7 +15328,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>12112</v>
       </c>
@@ -15380,7 +15402,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>12122</v>
       </c>
@@ -15454,7 +15476,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>11111</v>
       </c>
@@ -15528,7 +15550,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>12231</v>
       </c>
@@ -15602,7 +15624,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>23211</v>
       </c>
@@ -15676,7 +15698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>12111</v>
       </c>
@@ -15750,7 +15772,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>12132</v>
       </c>
@@ -15824,7 +15846,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>22232</v>
       </c>
@@ -15898,7 +15920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>12131</v>
       </c>
@@ -15972,7 +15994,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>21221</v>
       </c>
@@ -16046,7 +16068,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>12121</v>
       </c>
@@ -16120,7 +16142,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>11232</v>
       </c>
@@ -16194,7 +16216,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12211</v>
       </c>
@@ -16268,7 +16290,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>13121</v>
       </c>
@@ -16342,7 +16364,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>13112</v>
       </c>
@@ -16416,7 +16438,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>12212</v>
       </c>
@@ -16490,7 +16512,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>11132</v>
       </c>
@@ -16564,7 +16586,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>11211</v>
       </c>
@@ -16638,7 +16660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>11131</v>
       </c>
@@ -16712,7 +16734,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>11112</v>
       </c>
@@ -16786,7 +16808,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>21212</v>
       </c>
@@ -16860,7 +16882,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>11122</v>
       </c>
@@ -16934,7 +16956,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>21231</v>
       </c>
@@ -17008,7 +17030,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>22112</v>
       </c>
@@ -17082,7 +17104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>13122</v>
       </c>
@@ -17156,7 +17178,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>11222</v>
       </c>
@@ -17230,7 +17252,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>23111</v>
       </c>
@@ -17304,7 +17326,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>22221</v>
       </c>
@@ -17378,7 +17400,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>23231</v>
       </c>
@@ -17452,7 +17474,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>23132</v>
       </c>
@@ -17526,7 +17548,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>23222</v>
       </c>
@@ -17600,7 +17622,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>11231</v>
       </c>
@@ -17674,7 +17696,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>23232</v>
       </c>
@@ -17748,7 +17770,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>12221</v>
       </c>
@@ -17822,7 +17844,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>22231</v>
       </c>
@@ -17896,7 +17918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>23112</v>
       </c>
@@ -17970,7 +17992,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>23122</v>
       </c>
@@ -18050,4 +18072,5709 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC3DAC9-0E80-42AE-BB0F-4E8CB95E0FA3}">
+  <dimension ref="A1:J73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="15" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="43">
+        <v>21132</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="44">
+        <v>-2.446933</v>
+      </c>
+      <c r="H2" s="44">
+        <v>-4.989115</v>
+      </c>
+      <c r="I2" s="44">
+        <v>0.42802050000000003</v>
+      </c>
+      <c r="J2" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>13212</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="44">
+        <v>-2.3195579999999998</v>
+      </c>
+      <c r="H3" s="44">
+        <v>-4.8272599999999999</v>
+      </c>
+      <c r="I3" s="44">
+        <v>0.52894350000000001</v>
+      </c>
+      <c r="J3" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>12222</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="44">
+        <v>-2.3059460000000001</v>
+      </c>
+      <c r="H4" s="44">
+        <v>-4.6985320000000002</v>
+      </c>
+      <c r="I4" s="44">
+        <v>0.44500299999999998</v>
+      </c>
+      <c r="J4" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>21222</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="44">
+        <v>-1.907807</v>
+      </c>
+      <c r="H5" s="44">
+        <v>-5.3589409999999997</v>
+      </c>
+      <c r="I5" s="44">
+        <v>1.9895320000000001</v>
+      </c>
+      <c r="J5" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>23131</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="44">
+        <v>-1.330049</v>
+      </c>
+      <c r="H6" s="44">
+        <v>-4.722925</v>
+      </c>
+      <c r="I6" s="44">
+        <v>2.575396</v>
+      </c>
+      <c r="J6" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>13232</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="29">
+        <v>-1.29155</v>
+      </c>
+      <c r="H7" s="29">
+        <v>-4.3130050000000004</v>
+      </c>
+      <c r="I7" s="29">
+        <v>2.1811289999999999</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>13211</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="29">
+        <v>-1.1073059999999999</v>
+      </c>
+      <c r="H8" s="29">
+        <v>-3.8913660000000001</v>
+      </c>
+      <c r="I8" s="29">
+        <v>2.0092449999999999</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>23121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="29">
+        <v>-1.028051</v>
+      </c>
+      <c r="H9" s="29">
+        <v>-5.0038999999999998</v>
+      </c>
+      <c r="I9" s="29">
+        <v>3.345879</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>12232</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="29">
+        <v>-0.99674720000000006</v>
+      </c>
+      <c r="H10" s="29">
+        <v>-3.4294479999999998</v>
+      </c>
+      <c r="I10" s="29">
+        <v>1.825877</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>13222</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="29">
+        <v>-0.9631113</v>
+      </c>
+      <c r="H11" s="29">
+        <v>-4.2663890000000002</v>
+      </c>
+      <c r="I11" s="29">
+        <v>3.0576840000000001</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>13132</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="29">
+        <v>-0.93775439999999999</v>
+      </c>
+      <c r="H12" s="29">
+        <v>-3.342978</v>
+      </c>
+      <c r="I12" s="29">
+        <v>1.742021</v>
+      </c>
+      <c r="J12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>21121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="29">
+        <v>-0.90319459999999996</v>
+      </c>
+      <c r="H13" s="29">
+        <v>-3.576927</v>
+      </c>
+      <c r="I13" s="29">
+        <v>2.104552</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>21122</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="29">
+        <v>-0.87362300000000004</v>
+      </c>
+      <c r="H14" s="29">
+        <v>-3.5792869999999999</v>
+      </c>
+      <c r="I14" s="29">
+        <v>2.7280039999999999</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="29">
+        <v>-0.84597060000000002</v>
+      </c>
+      <c r="H15" s="29">
+        <v>-3.165092</v>
+      </c>
+      <c r="I15" s="29">
+        <v>1.6640250000000001</v>
+      </c>
+      <c r="J15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>22121</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="29">
+        <v>-0.81850060000000002</v>
+      </c>
+      <c r="H16" s="29">
+        <v>-3.575863</v>
+      </c>
+      <c r="I16" s="29">
+        <v>2.4675250000000002</v>
+      </c>
+      <c r="J16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>21232</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="29">
+        <v>-0.80846969999999996</v>
+      </c>
+      <c r="H17" s="29">
+        <v>-4.2389140000000003</v>
+      </c>
+      <c r="I17" s="29">
+        <v>3.2051229999999999</v>
+      </c>
+      <c r="J17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>13221</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="29">
+        <v>-0.76247469999999995</v>
+      </c>
+      <c r="H18" s="29">
+        <v>-3.822584</v>
+      </c>
+      <c r="I18" s="29">
+        <v>2.8336399999999999</v>
+      </c>
+      <c r="J18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>23212</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="29">
+        <v>-0.73896019999999996</v>
+      </c>
+      <c r="H19" s="29">
+        <v>-4.9088950000000002</v>
+      </c>
+      <c r="I19" s="29">
+        <v>4.3113159999999997</v>
+      </c>
+      <c r="J19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>21211</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="29">
+        <v>-0.72447850000000003</v>
+      </c>
+      <c r="H20" s="29">
+        <v>-3.8401909999999999</v>
+      </c>
+      <c r="I20" s="29">
+        <v>3.3518210000000002</v>
+      </c>
+      <c r="J20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>22211</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="29">
+        <v>-0.71577040000000003</v>
+      </c>
+      <c r="H21" s="29">
+        <v>-3.7413159999999999</v>
+      </c>
+      <c r="I21" s="29">
+        <v>2.8380649999999998</v>
+      </c>
+      <c r="J21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>13231</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="29">
+        <v>-0.69371899999999997</v>
+      </c>
+      <c r="H22" s="29">
+        <v>-3.8262290000000001</v>
+      </c>
+      <c r="I22" s="29">
+        <v>2.895032</v>
+      </c>
+      <c r="J22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="29">
+        <v>-0.66600579999999998</v>
+      </c>
+      <c r="H23" s="29">
+        <v>-3.6098520000000001</v>
+      </c>
+      <c r="I23" s="29">
+        <v>2.614128</v>
+      </c>
+      <c r="J23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22111</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="29">
+        <v>-0.66025310000000004</v>
+      </c>
+      <c r="H24" s="29">
+        <v>-2.8548260000000001</v>
+      </c>
+      <c r="I24" s="29">
+        <v>2.283436</v>
+      </c>
+      <c r="J24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>11121</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="29">
+        <v>-0.54657900000000004</v>
+      </c>
+      <c r="H25" s="29">
+        <v>-2.046627</v>
+      </c>
+      <c r="I25" s="29">
+        <v>1.278966</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>21131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="29">
+        <v>-0.34628110000000001</v>
+      </c>
+      <c r="H26" s="29">
+        <v>-2.8681169999999998</v>
+      </c>
+      <c r="I26" s="29">
+        <v>2.6195050000000002</v>
+      </c>
+      <c r="J26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21111</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="29">
+        <v>-0.3324841</v>
+      </c>
+      <c r="H27" s="29">
+        <v>-2.6410930000000001</v>
+      </c>
+      <c r="I27" s="29">
+        <v>2.563415</v>
+      </c>
+      <c r="J27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="29">
+        <v>-0.27472350000000001</v>
+      </c>
+      <c r="H28" s="29">
+        <v>-3.077137</v>
+      </c>
+      <c r="I28" s="29">
+        <v>2.914606</v>
+      </c>
+      <c r="J28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>13111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="29">
+        <v>-0.25772850000000003</v>
+      </c>
+      <c r="H29" s="29">
+        <v>-2.32403</v>
+      </c>
+      <c r="I29" s="29">
+        <v>2.2264699999999999</v>
+      </c>
+      <c r="J29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>11221</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="29">
+        <v>-0.23621549999999999</v>
+      </c>
+      <c r="H30" s="29">
+        <v>-2.713155</v>
+      </c>
+      <c r="I30" s="29">
+        <v>2.588063</v>
+      </c>
+      <c r="J30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>23221</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="29">
+        <v>-0.22467010000000001</v>
+      </c>
+      <c r="H31" s="29">
+        <v>-5.7010860000000001</v>
+      </c>
+      <c r="I31" s="29">
+        <v>5.5420540000000003</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>22212</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="29">
+        <v>-0.19975799999999999</v>
+      </c>
+      <c r="H32" s="29">
+        <v>-3.7899099999999999</v>
+      </c>
+      <c r="I32" s="29">
+        <v>3.620946</v>
+      </c>
+      <c r="J32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>22122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="29">
+        <v>-0.16936480000000001</v>
+      </c>
+      <c r="H33" s="29">
+        <v>-3.5583339999999999</v>
+      </c>
+      <c r="I33" s="29">
+        <v>3.5960670000000001</v>
+      </c>
+      <c r="J33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>22222</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="29">
+        <v>-0.1036062</v>
+      </c>
+      <c r="H34" s="29">
+        <v>-3.9677190000000002</v>
+      </c>
+      <c r="I34" s="29">
+        <v>4.1653260000000003</v>
+      </c>
+      <c r="J34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>11212</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="29">
+        <v>-9.3401999999999999E-2</v>
+      </c>
+      <c r="H35" s="29">
+        <v>-2.2959109999999998</v>
+      </c>
+      <c r="I35" s="29">
+        <v>2.5018419999999999</v>
+      </c>
+      <c r="J35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>21112</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="29">
+        <v>-7.9512700000000006E-2</v>
+      </c>
+      <c r="H36" s="29">
+        <v>-2.6419630000000001</v>
+      </c>
+      <c r="I36" s="29">
+        <v>2.843172</v>
+      </c>
+      <c r="J36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>12112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="29">
+        <v>-1.54815E-2</v>
+      </c>
+      <c r="H37" s="29">
+        <v>-1.820031</v>
+      </c>
+      <c r="I37" s="29">
+        <v>2.1191070000000001</v>
+      </c>
+      <c r="J37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>11111</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="29">
+        <v>2.0455000000000001E-2</v>
+      </c>
+      <c r="H38" s="29">
+        <v>-1.3384780000000001</v>
+      </c>
+      <c r="I38" s="29">
+        <v>1.825982</v>
+      </c>
+      <c r="J38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>21221</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="29">
+        <v>3.0313400000000001E-2</v>
+      </c>
+      <c r="H39" s="29">
+        <v>-3.8027060000000001</v>
+      </c>
+      <c r="I39" s="29">
+        <v>4.3123659999999999</v>
+      </c>
+      <c r="J39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>12132</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="29">
+        <v>8.1257300000000005E-2</v>
+      </c>
+      <c r="H40" s="29">
+        <v>-1.817021</v>
+      </c>
+      <c r="I40" s="29">
+        <v>2.4588209999999999</v>
+      </c>
+      <c r="J40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>12122</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="29">
+        <v>9.3646699999999999E-2</v>
+      </c>
+      <c r="H41" s="29">
+        <v>-1.943238</v>
+      </c>
+      <c r="I41" s="29">
+        <v>2.510259</v>
+      </c>
+      <c r="J41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>23211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="29">
+        <v>0.12103510000000001</v>
+      </c>
+      <c r="H42" s="29">
+        <v>-4.1226789999999998</v>
+      </c>
+      <c r="I42" s="29">
+        <v>5.3708280000000004</v>
+      </c>
+      <c r="J42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>12231</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="29">
+        <v>0.12676860000000001</v>
+      </c>
+      <c r="H43" s="29">
+        <v>-2.4340679999999999</v>
+      </c>
+      <c r="I43" s="29">
+        <v>3.1888930000000002</v>
+      </c>
+      <c r="J43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>22232</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="29">
+        <v>0.12796689999999999</v>
+      </c>
+      <c r="H44" s="29">
+        <v>-3.6614040000000001</v>
+      </c>
+      <c r="I44" s="29">
+        <v>4.306953</v>
+      </c>
+      <c r="J44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>12111</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="29">
+        <v>0.13487979999999999</v>
+      </c>
+      <c r="H45" s="29">
+        <v>-1.383097</v>
+      </c>
+      <c r="I45" s="29">
+        <v>2.03687</v>
+      </c>
+      <c r="J45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>12131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="29">
+        <v>0.14032510000000001</v>
+      </c>
+      <c r="H46" s="29">
+        <v>-1.508815</v>
+      </c>
+      <c r="I46" s="29">
+        <v>2.219983</v>
+      </c>
+      <c r="J46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>11232</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="29">
+        <v>0.32950839999999998</v>
+      </c>
+      <c r="H47" s="29">
+        <v>-2.051666</v>
+      </c>
+      <c r="I47" s="29">
+        <v>3.2122139999999999</v>
+      </c>
+      <c r="J47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>12211</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="29">
+        <v>0.41544799999999998</v>
+      </c>
+      <c r="H48" s="29">
+        <v>-1.836368</v>
+      </c>
+      <c r="I48" s="29">
+        <v>3.1959879999999998</v>
+      </c>
+      <c r="J48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>12121</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="29">
+        <v>0.4301991</v>
+      </c>
+      <c r="H49" s="29">
+        <v>-1.43231</v>
+      </c>
+      <c r="I49" s="29">
+        <v>2.7420599999999999</v>
+      </c>
+      <c r="J49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>13121</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="29">
+        <v>0.43596699999999999</v>
+      </c>
+      <c r="H50" s="29">
+        <v>-2.2422970000000002</v>
+      </c>
+      <c r="I50" s="29">
+        <v>3.8868680000000002</v>
+      </c>
+      <c r="J50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>12212</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="29">
+        <v>0.47054220000000002</v>
+      </c>
+      <c r="H51" s="29">
+        <v>-1.982572</v>
+      </c>
+      <c r="I51" s="29">
+        <v>3.2697409999999998</v>
+      </c>
+      <c r="J51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>13112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="29">
+        <v>0.54402510000000004</v>
+      </c>
+      <c r="H52" s="29">
+        <v>-2.0295000000000001</v>
+      </c>
+      <c r="I52" s="29">
+        <v>3.5350429999999999</v>
+      </c>
+      <c r="J52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>11132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="29">
+        <v>0.5927867</v>
+      </c>
+      <c r="H53" s="29">
+        <v>-1.262489</v>
+      </c>
+      <c r="I53" s="29">
+        <v>2.7943699999999998</v>
+      </c>
+      <c r="J53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>11211</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="29">
+        <v>0.6350095</v>
+      </c>
+      <c r="H54" s="29">
+        <v>-1.473517</v>
+      </c>
+      <c r="I54" s="29">
+        <v>3.3785029999999998</v>
+      </c>
+      <c r="J54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>11112</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="29">
+        <v>0.72103280000000003</v>
+      </c>
+      <c r="H55" s="29">
+        <v>-1.097269</v>
+      </c>
+      <c r="I55" s="29">
+        <v>2.7827259999999998</v>
+      </c>
+      <c r="J55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>21231</v>
+      </c>
+      <c r="B56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="29">
+        <v>0.73625379999999996</v>
+      </c>
+      <c r="H56" s="29">
+        <v>-2.6793520000000002</v>
+      </c>
+      <c r="I56" s="29">
+        <v>4.5172610000000004</v>
+      </c>
+      <c r="J56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>11131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="29">
+        <v>0.73688140000000002</v>
+      </c>
+      <c r="H57" s="29">
+        <v>-1.0515650000000001</v>
+      </c>
+      <c r="I57" s="29">
+        <v>3.042243</v>
+      </c>
+      <c r="J57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>21212</v>
+      </c>
+      <c r="B58" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="29">
+        <v>0.88734389999999996</v>
+      </c>
+      <c r="H58" s="29">
+        <v>-2.644272</v>
+      </c>
+      <c r="I58" s="29">
+        <v>4.9767330000000003</v>
+      </c>
+      <c r="J58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>11122</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="29">
+        <v>0.97206060000000005</v>
+      </c>
+      <c r="H59" s="29">
+        <v>-1.140701</v>
+      </c>
+      <c r="I59" s="29">
+        <v>3.6049310000000001</v>
+      </c>
+      <c r="J59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>22112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="29">
+        <v>1.0328809999999999</v>
+      </c>
+      <c r="H60" s="29">
+        <v>-2.1596869999999999</v>
+      </c>
+      <c r="I60" s="29">
+        <v>4.429824</v>
+      </c>
+      <c r="J60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>13122</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" s="29">
+        <v>1.044842</v>
+      </c>
+      <c r="H61" s="29">
+        <v>-2.0938029999999999</v>
+      </c>
+      <c r="I61" s="29">
+        <v>4.5078649999999998</v>
+      </c>
+      <c r="J61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>11222</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="29">
+        <v>1.435619</v>
+      </c>
+      <c r="H62" s="29">
+        <v>-1.5622240000000001</v>
+      </c>
+      <c r="I62" s="29">
+        <v>4.7029909999999999</v>
+      </c>
+      <c r="J62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>22221</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="29">
+        <v>1.6631899999999999</v>
+      </c>
+      <c r="H63" s="29">
+        <v>-2.507063</v>
+      </c>
+      <c r="I63" s="29">
+        <v>6.4980159999999998</v>
+      </c>
+      <c r="J63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>23111</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="29">
+        <v>1.6650659999999999</v>
+      </c>
+      <c r="H64" s="29">
+        <v>-2.0055049999999999</v>
+      </c>
+      <c r="I64" s="29">
+        <v>6.2566940000000004</v>
+      </c>
+      <c r="J64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>23132</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="29">
+        <v>1.9069529999999999</v>
+      </c>
+      <c r="H65" s="29">
+        <v>-2.157823</v>
+      </c>
+      <c r="I65" s="29">
+        <v>6.0785470000000004</v>
+      </c>
+      <c r="J65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>23222</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="29">
+        <v>2.0187050000000002</v>
+      </c>
+      <c r="H66" s="29">
+        <v>-2.6930860000000001</v>
+      </c>
+      <c r="I66" s="29">
+        <v>7.1182270000000001</v>
+      </c>
+      <c r="J66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>23231</v>
+      </c>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="29">
+        <v>2.041455</v>
+      </c>
+      <c r="H67" s="29">
+        <v>-2.8436819999999998</v>
+      </c>
+      <c r="I67" s="29">
+        <v>7.5218480000000003</v>
+      </c>
+      <c r="J67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>11231</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="29">
+        <v>2.177619</v>
+      </c>
+      <c r="H68" s="29">
+        <v>-0.40295120000000001</v>
+      </c>
+      <c r="I68" s="29">
+        <v>5.3077899999999998</v>
+      </c>
+      <c r="J68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>23232</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" s="30">
+        <v>2.2827199999999999</v>
+      </c>
+      <c r="H69" s="30">
+        <v>-2.537512</v>
+      </c>
+      <c r="I69" s="30">
+        <v>7.1089820000000001</v>
+      </c>
+      <c r="J69" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>12221</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="30">
+        <v>2.3454480000000002</v>
+      </c>
+      <c r="H70" s="30">
+        <v>-0.62905690000000003</v>
+      </c>
+      <c r="I70" s="30">
+        <v>5.6914930000000004</v>
+      </c>
+      <c r="J70" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>22231</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="30">
+        <v>3.003714</v>
+      </c>
+      <c r="H71" s="30">
+        <v>-0.72237209999999996</v>
+      </c>
+      <c r="I71" s="30">
+        <v>7.2871230000000002</v>
+      </c>
+      <c r="J71" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>23112</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" s="30">
+        <v>3.4696280000000002</v>
+      </c>
+      <c r="H72" s="30">
+        <v>-0.8496165</v>
+      </c>
+      <c r="I72" s="30">
+        <v>8.6137650000000008</v>
+      </c>
+      <c r="J72" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>23122</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" s="30">
+        <v>3.870079</v>
+      </c>
+      <c r="H73" s="30">
+        <v>-0.74056630000000001</v>
+      </c>
+      <c r="I73" s="30">
+        <v>9.2399450000000005</v>
+      </c>
+      <c r="J73" s="2">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3164BB4C-4C8A-475B-87E9-838283850749}">
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>13212</v>
+      </c>
+      <c r="B2" s="1">
+        <v>347</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>21132</v>
+      </c>
+      <c r="K2" t="str">
+        <f>_xlfn.XLOOKUP(I2, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L2" t="str">
+        <f>_xlfn.XLOOKUP(I2, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M2" t="str">
+        <f>_xlfn.XLOOKUP(I2, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N2" t="str">
+        <f>_xlfn.XLOOKUP(I2, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O2" t="str">
+        <f>_xlfn.XLOOKUP(I2, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>21132</v>
+      </c>
+      <c r="B3" s="1">
+        <v>514</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3">
+        <v>13212</v>
+      </c>
+      <c r="K3" t="str">
+        <f>_xlfn.XLOOKUP(I3, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L3" t="str">
+        <f>_xlfn.XLOOKUP(I3, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M3" t="str">
+        <f>_xlfn.XLOOKUP(I3, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N3" t="str">
+        <f>_xlfn.XLOOKUP(I3, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O3" t="str">
+        <f>_xlfn.XLOOKUP(I3, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>12222</v>
+      </c>
+      <c r="B4" s="1">
+        <v>364</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4">
+        <v>12222</v>
+      </c>
+      <c r="K4" t="str">
+        <f>_xlfn.XLOOKUP(I4, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L4" t="str">
+        <f>_xlfn.XLOOKUP(I4, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M4" t="str">
+        <f>_xlfn.XLOOKUP(I4, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N4" t="str">
+        <f>_xlfn.XLOOKUP(I4, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O4" t="str">
+        <f>_xlfn.XLOOKUP(I4, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>21222</v>
+      </c>
+      <c r="B5" s="1">
+        <v>399</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>21222</v>
+      </c>
+      <c r="K5" t="str">
+        <f>_xlfn.XLOOKUP(I5, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L5" t="str">
+        <f>_xlfn.XLOOKUP(I5, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M5" t="str">
+        <f>_xlfn.XLOOKUP(I5, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N5" t="str">
+        <f>_xlfn.XLOOKUP(I5, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O5" t="str">
+        <f>_xlfn.XLOOKUP(I5, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>13232</v>
+      </c>
+      <c r="B6" s="1">
+        <v>543</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>23131</v>
+      </c>
+      <c r="K6" t="str">
+        <f>_xlfn.XLOOKUP(I6, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L6" t="str">
+        <f>_xlfn.XLOOKUP(I6, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M6" t="str">
+        <f>_xlfn.XLOOKUP(I6, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N6" t="str">
+        <f>_xlfn.XLOOKUP(I6, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O6" t="str">
+        <f>_xlfn.XLOOKUP(I6, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>23131</v>
+      </c>
+      <c r="B7">
+        <v>222</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>13232</v>
+      </c>
+      <c r="K7" t="str">
+        <f>_xlfn.XLOOKUP(I7, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L7" t="str">
+        <f>_xlfn.XLOOKUP(I7, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M7" t="str">
+        <f>_xlfn.XLOOKUP(I7, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N7" t="str">
+        <f>_xlfn.XLOOKUP(I7, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O7" t="str">
+        <f>_xlfn.XLOOKUP(I7, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>13211</v>
+      </c>
+      <c r="B8">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>13211</v>
+      </c>
+      <c r="K8" t="str">
+        <f>_xlfn.XLOOKUP(I8, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L8" t="str">
+        <f>_xlfn.XLOOKUP(I8, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M8" t="str">
+        <f>_xlfn.XLOOKUP(I8, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N8" t="str">
+        <f>_xlfn.XLOOKUP(I8, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O8" t="str">
+        <f>_xlfn.XLOOKUP(I8, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>13222</v>
+      </c>
+      <c r="B9">
+        <v>377</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>23121</v>
+      </c>
+      <c r="K9" t="str">
+        <f>_xlfn.XLOOKUP(I9, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L9" t="str">
+        <f>_xlfn.XLOOKUP(I9, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M9" t="str">
+        <f>_xlfn.XLOOKUP(I9, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N9" t="str">
+        <f>_xlfn.XLOOKUP(I9, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O9" t="str">
+        <f>_xlfn.XLOOKUP(I9, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>23121</v>
+      </c>
+      <c r="B10">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10">
+        <v>12232</v>
+      </c>
+      <c r="K10" t="str">
+        <f>_xlfn.XLOOKUP(I10, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L10" t="str">
+        <f>_xlfn.XLOOKUP(I10, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M10" t="str">
+        <f>_xlfn.XLOOKUP(I10, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N10" t="str">
+        <f>_xlfn.XLOOKUP(I10, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O10" t="str">
+        <f>_xlfn.XLOOKUP(I10, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>12232</v>
+      </c>
+      <c r="B11">
+        <v>511</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>13222</v>
+      </c>
+      <c r="K11" t="str">
+        <f>_xlfn.XLOOKUP(I11, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L11" t="str">
+        <f>_xlfn.XLOOKUP(I11, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M11" t="str">
+        <f>_xlfn.XLOOKUP(I11, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N11" t="str">
+        <f>_xlfn.XLOOKUP(I11, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O11" t="str">
+        <f>_xlfn.XLOOKUP(I11, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>21121</v>
+      </c>
+      <c r="B12">
+        <v>128</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12">
+        <v>13132</v>
+      </c>
+      <c r="K12" t="str">
+        <f>_xlfn.XLOOKUP(I12, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L12" t="str">
+        <f>_xlfn.XLOOKUP(I12, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M12" t="str">
+        <f>_xlfn.XLOOKUP(I12, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N12" t="str">
+        <f>_xlfn.XLOOKUP(I12, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O12" t="str">
+        <f>_xlfn.XLOOKUP(I12, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13131</v>
+      </c>
+      <c r="B13">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13">
+        <v>21121</v>
+      </c>
+      <c r="K13" t="str">
+        <f>_xlfn.XLOOKUP(I13, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L13" t="str">
+        <f>_xlfn.XLOOKUP(I13, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M13" t="str">
+        <f>_xlfn.XLOOKUP(I13, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N13" t="str">
+        <f>_xlfn.XLOOKUP(I13, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O13" t="str">
+        <f>_xlfn.XLOOKUP(I13, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13231</v>
+      </c>
+      <c r="B14">
+        <v>225</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14">
+        <v>21122</v>
+      </c>
+      <c r="K14" t="str">
+        <f>_xlfn.XLOOKUP(I14, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L14" t="str">
+        <f>_xlfn.XLOOKUP(I14, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M14" t="str">
+        <f>_xlfn.XLOOKUP(I14, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N14" t="str">
+        <f>_xlfn.XLOOKUP(I14, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O14" t="str">
+        <f>_xlfn.XLOOKUP(I14, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>22121</v>
+      </c>
+      <c r="B15">
+        <v>128</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>13131</v>
+      </c>
+      <c r="K15" t="str">
+        <f>_xlfn.XLOOKUP(I15, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L15" t="str">
+        <f>_xlfn.XLOOKUP(I15, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M15" t="str">
+        <f>_xlfn.XLOOKUP(I15, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N15" t="str">
+        <f>_xlfn.XLOOKUP(I15, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O15" t="str">
+        <f>_xlfn.XLOOKUP(I15, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>13221</v>
+      </c>
+      <c r="B16">
+        <v>192</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16">
+        <v>22121</v>
+      </c>
+      <c r="K16" t="str">
+        <f>_xlfn.XLOOKUP(I16, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L16" t="str">
+        <f>_xlfn.XLOOKUP(I16, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M16" t="str">
+        <f>_xlfn.XLOOKUP(I16, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N16" t="str">
+        <f>_xlfn.XLOOKUP(I16, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O16" t="str">
+        <f>_xlfn.XLOOKUP(I16, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>13132</v>
+      </c>
+      <c r="B17">
+        <v>497</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>21232</v>
+      </c>
+      <c r="K17" t="str">
+        <f>_xlfn.XLOOKUP(I17, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L17" t="str">
+        <f>_xlfn.XLOOKUP(I17, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M17" t="str">
+        <f>_xlfn.XLOOKUP(I17, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N17" t="str">
+        <f>_xlfn.XLOOKUP(I17, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O17" t="str">
+        <f>_xlfn.XLOOKUP(I17, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>21122</v>
+      </c>
+      <c r="B18">
+        <v>307</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18">
+        <v>13221</v>
+      </c>
+      <c r="K18" t="str">
+        <f>_xlfn.XLOOKUP(I18, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L18" t="str">
+        <f>_xlfn.XLOOKUP(I18, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M18" t="str">
+        <f>_xlfn.XLOOKUP(I18, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N18" t="str">
+        <f>_xlfn.XLOOKUP(I18, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O18" t="str">
+        <f>_xlfn.XLOOKUP(I18, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>22111</v>
+      </c>
+      <c r="B19">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19">
+        <v>23212</v>
+      </c>
+      <c r="K19" t="str">
+        <f>_xlfn.XLOOKUP(I19, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L19" t="str">
+        <f>_xlfn.XLOOKUP(I19, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M19" t="str">
+        <f>_xlfn.XLOOKUP(I19, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N19" t="str">
+        <f>_xlfn.XLOOKUP(I19, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O19" t="str">
+        <f>_xlfn.XLOOKUP(I19, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>22211</v>
+      </c>
+      <c r="B20">
+        <v>144</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20">
+        <v>21211</v>
+      </c>
+      <c r="K20" t="str">
+        <f>_xlfn.XLOOKUP(I20, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L20" t="str">
+        <f>_xlfn.XLOOKUP(I20, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M20" t="str">
+        <f>_xlfn.XLOOKUP(I20, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N20" t="str">
+        <f>_xlfn.XLOOKUP(I20, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O20" t="str">
+        <f>_xlfn.XLOOKUP(I20, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21232</v>
+      </c>
+      <c r="B21">
+        <v>544</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21">
+        <v>22211</v>
+      </c>
+      <c r="K21" t="str">
+        <f>_xlfn.XLOOKUP(I21, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L21" t="str">
+        <f>_xlfn.XLOOKUP(I21, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M21" t="str">
+        <f>_xlfn.XLOOKUP(I21, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N21" t="str">
+        <f>_xlfn.XLOOKUP(I21, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O21" t="str">
+        <f>_xlfn.XLOOKUP(I21, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21211</v>
+      </c>
+      <c r="B22">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22">
+        <v>13231</v>
+      </c>
+      <c r="K22" t="str">
+        <f>_xlfn.XLOOKUP(I22, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L22" t="str">
+        <f>_xlfn.XLOOKUP(I22, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M22" t="str">
+        <f>_xlfn.XLOOKUP(I22, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N22" t="str">
+        <f>_xlfn.XLOOKUP(I22, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O22" t="str">
+        <f>_xlfn.XLOOKUP(I22, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>23212</v>
+      </c>
+      <c r="B23">
+        <v>314</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23">
+        <v>22132</v>
+      </c>
+      <c r="K23" t="str">
+        <f>_xlfn.XLOOKUP(I23, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L23" t="str">
+        <f>_xlfn.XLOOKUP(I23, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M23" t="str">
+        <f>_xlfn.XLOOKUP(I23, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N23" t="str">
+        <f>_xlfn.XLOOKUP(I23, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O23" t="str">
+        <f>_xlfn.XLOOKUP(I23, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22132</v>
+      </c>
+      <c r="B24">
+        <v>418</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24">
+        <v>22111</v>
+      </c>
+      <c r="K24" t="str">
+        <f>_xlfn.XLOOKUP(I24, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L24" t="str">
+        <f>_xlfn.XLOOKUP(I24, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M24" t="str">
+        <f>_xlfn.XLOOKUP(I24, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N24" t="str">
+        <f>_xlfn.XLOOKUP(I24, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O24" t="str">
+        <f>_xlfn.XLOOKUP(I24, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>11121</v>
+      </c>
+      <c r="B25">
+        <v>151</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <v>11121</v>
+      </c>
+      <c r="K25" t="str">
+        <f>_xlfn.XLOOKUP(I25, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L25" t="str">
+        <f>_xlfn.XLOOKUP(I25, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M25" t="str">
+        <f>_xlfn.XLOOKUP(I25, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N25" t="str">
+        <f>_xlfn.XLOOKUP(I25, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O25" t="str">
+        <f>_xlfn.XLOOKUP(I25, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23221</v>
+      </c>
+      <c r="B26">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26">
+        <v>21131</v>
+      </c>
+      <c r="K26" t="str">
+        <f>_xlfn.XLOOKUP(I26, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L26" t="str">
+        <f>_xlfn.XLOOKUP(I26, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M26" t="str">
+        <f>_xlfn.XLOOKUP(I26, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N26" t="str">
+        <f>_xlfn.XLOOKUP(I26, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O26" t="str">
+        <f>_xlfn.XLOOKUP(I26, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>22212</v>
+      </c>
+      <c r="B27">
+        <v>308</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27">
+        <v>21111</v>
+      </c>
+      <c r="K27" t="str">
+        <f>_xlfn.XLOOKUP(I27, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L27" t="str">
+        <f>_xlfn.XLOOKUP(I27,A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M27" t="str">
+        <f>_xlfn.XLOOKUP(I27, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N27" t="str">
+        <f>_xlfn.XLOOKUP(I27, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O27" t="str">
+        <f>_xlfn.XLOOKUP(I27, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>21111</v>
+      </c>
+      <c r="B28">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28">
+        <v>22131</v>
+      </c>
+      <c r="K28" t="str">
+        <f>_xlfn.XLOOKUP(I28, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L28" t="str">
+        <f>_xlfn.XLOOKUP(I28, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M28" t="str">
+        <f>_xlfn.XLOOKUP(I28, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N28" t="str">
+        <f>_xlfn.XLOOKUP(I28, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O28" t="str">
+        <f>_xlfn.XLOOKUP(I28, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>22131</v>
+      </c>
+      <c r="B29">
+        <v>244</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29">
+        <v>13111</v>
+      </c>
+      <c r="K29" t="str">
+        <f>_xlfn.XLOOKUP(I29, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L29" t="str">
+        <f>_xlfn.XLOOKUP(I29, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M29" t="str">
+        <f>_xlfn.XLOOKUP(I29, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N29" t="str">
+        <f>_xlfn.XLOOKUP(I29, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O29" t="str">
+        <f>_xlfn.XLOOKUP(I29, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>22222</v>
+      </c>
+      <c r="B30">
+        <v>336</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30">
+        <v>11221</v>
+      </c>
+      <c r="K30" t="str">
+        <f>_xlfn.XLOOKUP(I30, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L30" t="str">
+        <f>_xlfn.XLOOKUP(I30, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M30" t="str">
+        <f>_xlfn.XLOOKUP(I30, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N30" t="str">
+        <f>_xlfn.XLOOKUP(I30, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O30" t="str">
+        <f>_xlfn.XLOOKUP(I30, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>13111</v>
+      </c>
+      <c r="B31">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31">
+        <v>23221</v>
+      </c>
+      <c r="K31" t="str">
+        <f>_xlfn.XLOOKUP(I31, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L31" t="str">
+        <f>_xlfn.XLOOKUP(I31, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M31" t="str">
+        <f>_xlfn.XLOOKUP(I31, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N31" t="str">
+        <f>_xlfn.XLOOKUP(I31, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O31" t="str">
+        <f>_xlfn.XLOOKUP(I31, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>11221</v>
+      </c>
+      <c r="B32">
+        <v>222</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32">
+        <v>22212</v>
+      </c>
+      <c r="K32" t="str">
+        <f>_xlfn.XLOOKUP(I32, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L32" t="str">
+        <f>_xlfn.XLOOKUP(I32, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M32" t="str">
+        <f>_xlfn.XLOOKUP(I32, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N32" t="str">
+        <f>_xlfn.XLOOKUP(I32, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O32" t="str">
+        <f>_xlfn.XLOOKUP(I32, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>22122</v>
+      </c>
+      <c r="B33">
+        <v>232</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33">
+        <v>22122</v>
+      </c>
+      <c r="K33" t="str">
+        <f>_xlfn.XLOOKUP(I33, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L33" t="str">
+        <f>_xlfn.XLOOKUP(I33, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M33" t="str">
+        <f>_xlfn.XLOOKUP(I33, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N33" t="str">
+        <f>_xlfn.XLOOKUP(I33, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O33" t="str">
+        <f>_xlfn.XLOOKUP(I33, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>21131</v>
+      </c>
+      <c r="B34">
+        <v>265</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34">
+        <v>22222</v>
+      </c>
+      <c r="K34" t="str">
+        <f>_xlfn.XLOOKUP(I34, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L34" t="str">
+        <f>_xlfn.XLOOKUP(I34, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M34" t="str">
+        <f>_xlfn.XLOOKUP(I34, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N34" t="str">
+        <f>_xlfn.XLOOKUP(I34, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O34" t="str">
+        <f>_xlfn.XLOOKUP(I34, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>21112</v>
+      </c>
+      <c r="B35">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35">
+        <v>11212</v>
+      </c>
+      <c r="K35" t="str">
+        <f>_xlfn.XLOOKUP(I35, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L35" t="str">
+        <f>_xlfn.XLOOKUP(I35, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M35" t="str">
+        <f>_xlfn.XLOOKUP(I35, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N35" t="str">
+        <f>_xlfn.XLOOKUP(I35, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O35" t="str">
+        <f>_xlfn.XLOOKUP(I35, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>11212</v>
+      </c>
+      <c r="B36">
+        <v>350</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36">
+        <v>21112</v>
+      </c>
+      <c r="K36" t="str">
+        <f>_xlfn.XLOOKUP(I36, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L36" t="str">
+        <f>_xlfn.XLOOKUP(I36, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M36" t="str">
+        <f>_xlfn.XLOOKUP(I36, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N36" t="str">
+        <f>_xlfn.XLOOKUP(I36, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O36" t="str">
+        <f>_xlfn.XLOOKUP(I36, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>12112</v>
+      </c>
+      <c r="B37">
+        <v>191</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37">
+        <v>12112</v>
+      </c>
+      <c r="K37" t="str">
+        <f>_xlfn.XLOOKUP(I37, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L37" t="str">
+        <f>_xlfn.XLOOKUP(I37, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M37" t="str">
+        <f>_xlfn.XLOOKUP(I37, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N37" t="str">
+        <f>_xlfn.XLOOKUP(I37,A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O37" t="str">
+        <f>_xlfn.XLOOKUP(I37, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>12122</v>
+      </c>
+      <c r="B38">
+        <v>230</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38">
+        <v>11111</v>
+      </c>
+      <c r="K38" t="str">
+        <f>_xlfn.XLOOKUP(I38, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L38" t="str">
+        <f>_xlfn.XLOOKUP(I38, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M38" t="str">
+        <f>_xlfn.XLOOKUP(I38, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N38" t="str">
+        <f>_xlfn.XLOOKUP(I38, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O38" t="str">
+        <f>_xlfn.XLOOKUP(I38, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>11111</v>
+      </c>
+      <c r="B39">
+        <v>75</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39">
+        <v>21221</v>
+      </c>
+      <c r="K39" t="str">
+        <f>_xlfn.XLOOKUP(I39, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L39" t="str">
+        <f>_xlfn.XLOOKUP(I39, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M39" t="str">
+        <f>_xlfn.XLOOKUP(I39, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N39" t="str">
+        <f>_xlfn.XLOOKUP(I39, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O39" t="str">
+        <f>_xlfn.XLOOKUP(I39, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>12231</v>
+      </c>
+      <c r="B40">
+        <v>286</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40">
+        <v>12132</v>
+      </c>
+      <c r="K40" t="str">
+        <f>_xlfn.XLOOKUP(I40, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L40" t="str">
+        <f>_xlfn.XLOOKUP(I40, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M40" t="str">
+        <f>_xlfn.XLOOKUP(I40, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N40" t="str">
+        <f>_xlfn.XLOOKUP(I40, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O40" t="str">
+        <f>_xlfn.XLOOKUP(I40, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>23211</v>
+      </c>
+      <c r="B41">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41">
+        <v>12122</v>
+      </c>
+      <c r="K41" t="str">
+        <f>_xlfn.XLOOKUP(I41, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L41" t="str">
+        <f>_xlfn.XLOOKUP(I41, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M41" t="str">
+        <f>_xlfn.XLOOKUP(I41, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N41" t="str">
+        <f>_xlfn.XLOOKUP(I41, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O41" t="str">
+        <f>_xlfn.XLOOKUP(I41, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>12111</v>
+      </c>
+      <c r="B42">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42">
+        <v>23211</v>
+      </c>
+      <c r="K42" t="str">
+        <f>_xlfn.XLOOKUP(I42, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L42" t="str">
+        <f>_xlfn.XLOOKUP(I42, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M42" t="str">
+        <f>_xlfn.XLOOKUP(I42, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N42" t="str">
+        <f>_xlfn.XLOOKUP(I42, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O42" t="str">
+        <f>_xlfn.XLOOKUP(I42, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>12132</v>
+      </c>
+      <c r="B43">
+        <v>494</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43">
+        <v>12231</v>
+      </c>
+      <c r="K43" t="str">
+        <f>_xlfn.XLOOKUP(I43, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L43" t="str">
+        <f>_xlfn.XLOOKUP(I43, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M43" t="str">
+        <f>_xlfn.XLOOKUP(I43, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N43" t="str">
+        <f>_xlfn.XLOOKUP(I43, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O43" t="str">
+        <f>_xlfn.XLOOKUP(I43, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>22232</v>
+      </c>
+      <c r="B44">
+        <v>472</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44">
+        <v>22232</v>
+      </c>
+      <c r="K44" t="str">
+        <f>_xlfn.XLOOKUP(I44, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L44" t="str">
+        <f>_xlfn.XLOOKUP(I44, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M44" t="str">
+        <f>_xlfn.XLOOKUP(I44, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N44" t="str">
+        <f>_xlfn.XLOOKUP(I44, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O44" t="str">
+        <f>_xlfn.XLOOKUP(I44, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>12131</v>
+      </c>
+      <c r="B45">
+        <v>251</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45">
+        <v>12111</v>
+      </c>
+      <c r="K45" t="str">
+        <f>_xlfn.XLOOKUP(I45, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L45" t="str">
+        <f>_xlfn.XLOOKUP(I45, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M45" t="str">
+        <f>_xlfn.XLOOKUP(I45, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N45" t="str">
+        <f>_xlfn.XLOOKUP(I45, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O45" t="str">
+        <f>_xlfn.XLOOKUP(I45, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>21221</v>
+      </c>
+      <c r="B46">
+        <v>221</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46">
+        <v>12131</v>
+      </c>
+      <c r="K46" t="str">
+        <f>_xlfn.XLOOKUP(I46, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L46" t="str">
+        <f>_xlfn.XLOOKUP(I46, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M46" t="str">
+        <f>_xlfn.XLOOKUP(I46, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N46" t="str">
+        <f>_xlfn.XLOOKUP(I46, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O46" t="str">
+        <f>_xlfn.XLOOKUP(I46, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>12121</v>
+      </c>
+      <c r="B47">
+        <v>137</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47">
+        <v>11232</v>
+      </c>
+      <c r="K47" t="str">
+        <f>_xlfn.XLOOKUP(I47, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L47" t="str">
+        <f>_xlfn.XLOOKUP(I47, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M47" t="str">
+        <f>_xlfn.XLOOKUP(I47, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N47" t="str">
+        <f>_xlfn.XLOOKUP(I47,A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O47" t="str">
+        <f>_xlfn.XLOOKUP(I47, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>11232</v>
+      </c>
+      <c r="B48">
+        <v>560</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48">
+        <v>12211</v>
+      </c>
+      <c r="K48" t="str">
+        <f>_xlfn.XLOOKUP(I48, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L48" t="str">
+        <f>_xlfn.XLOOKUP(I48, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M48" t="str">
+        <f>_xlfn.XLOOKUP(I48, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N48" t="str">
+        <f>_xlfn.XLOOKUP(I48, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O48" t="str">
+        <f>_xlfn.XLOOKUP(I48, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>12211</v>
+      </c>
+      <c r="B49">
+        <v>147</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49">
+        <v>12121</v>
+      </c>
+      <c r="K49" t="str">
+        <f>_xlfn.XLOOKUP(I49, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L49" t="str">
+        <f>_xlfn.XLOOKUP(I49, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M49" t="str">
+        <f>_xlfn.XLOOKUP(I49, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N49" t="str">
+        <f>_xlfn.XLOOKUP(I49, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O49" t="str">
+        <f>_xlfn.XLOOKUP(I49, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>13121</v>
+      </c>
+      <c r="B50">
+        <v>107</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50">
+        <v>13121</v>
+      </c>
+      <c r="K50" t="str">
+        <f>_xlfn.XLOOKUP(I50, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L50" t="str">
+        <f>_xlfn.XLOOKUP(I50, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M50" t="str">
+        <f>_xlfn.XLOOKUP(I50, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N50" t="str">
+        <f>_xlfn.XLOOKUP(I50, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O50" t="str">
+        <f>_xlfn.XLOOKUP(I50, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>13112</v>
+      </c>
+      <c r="B51">
+        <v>201</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51">
+        <v>12212</v>
+      </c>
+      <c r="K51" t="str">
+        <f>_xlfn.XLOOKUP(I51, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L51" t="str">
+        <f>_xlfn.XLOOKUP(I51, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M51" t="str">
+        <f>_xlfn.XLOOKUP(I51, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N51" t="str">
+        <f>_xlfn.XLOOKUP(I51, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O51" t="str">
+        <f>_xlfn.XLOOKUP(I51, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>12212</v>
+      </c>
+      <c r="B52">
+        <v>307</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52">
+        <v>13112</v>
+      </c>
+      <c r="K52" t="str">
+        <f>_xlfn.XLOOKUP(I52, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L52" t="str">
+        <f>_xlfn.XLOOKUP(I52, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M52" t="str">
+        <f>_xlfn.XLOOKUP(I52, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N52" t="str">
+        <f>_xlfn.XLOOKUP(I52, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O52" t="str">
+        <f>_xlfn.XLOOKUP(I52, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>11132</v>
+      </c>
+      <c r="B53">
+        <v>541</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53">
+        <v>11132</v>
+      </c>
+      <c r="K53" t="str">
+        <f>_xlfn.XLOOKUP(I53, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L53" t="str">
+        <f>_xlfn.XLOOKUP(I53, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M53" t="str">
+        <f>_xlfn.XLOOKUP(I53, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N53" t="str">
+        <f>_xlfn.XLOOKUP(I53, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O53" t="str">
+        <f>_xlfn.XLOOKUP(I53, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>11211</v>
+      </c>
+      <c r="B54">
+        <v>168</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54">
+        <v>11211</v>
+      </c>
+      <c r="K54" t="str">
+        <f>_xlfn.XLOOKUP(I54, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L54" t="str">
+        <f>_xlfn.XLOOKUP(I54, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M54" t="str">
+        <f>_xlfn.XLOOKUP(I54, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N54" t="str">
+        <f>_xlfn.XLOOKUP(I54, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O54" t="str">
+        <f>_xlfn.XLOOKUP(I54, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>11131</v>
+      </c>
+      <c r="B55">
+        <v>268</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55">
+        <v>11112</v>
+      </c>
+      <c r="K55" t="str">
+        <f>_xlfn.XLOOKUP(I55, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L55" t="str">
+        <f>_xlfn.XLOOKUP(I55, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M55" t="str">
+        <f>_xlfn.XLOOKUP(I55, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N55" t="str">
+        <f>_xlfn.XLOOKUP(I55, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O55" t="str">
+        <f>_xlfn.XLOOKUP(I55, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>11112</v>
+      </c>
+      <c r="B56">
+        <v>263</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56">
+        <v>21231</v>
+      </c>
+      <c r="K56" t="str">
+        <f>_xlfn.XLOOKUP(I56, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L56" t="str">
+        <f>_xlfn.XLOOKUP(I56, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M56" t="str">
+        <f>_xlfn.XLOOKUP(I56, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N56" t="str">
+        <f>_xlfn.XLOOKUP(I56, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O56" t="str">
+        <f>_xlfn.XLOOKUP(I56, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>21212</v>
+      </c>
+      <c r="B57">
+        <v>338</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57">
+        <v>11131</v>
+      </c>
+      <c r="K57" t="str">
+        <f>_xlfn.XLOOKUP(I57, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L57" t="str">
+        <f>_xlfn.XLOOKUP(I57, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M57" t="str">
+        <f>_xlfn.XLOOKUP(I57, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N57" t="str">
+        <f>_xlfn.XLOOKUP(I57, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O57" t="str">
+        <f>_xlfn.XLOOKUP(I57, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>11122</v>
+      </c>
+      <c r="B58">
+        <v>267</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58">
+        <v>21212</v>
+      </c>
+      <c r="K58" t="str">
+        <f>_xlfn.XLOOKUP(I58, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L58" t="str">
+        <f>_xlfn.XLOOKUP(I58, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M58" t="str">
+        <f>_xlfn.XLOOKUP(I58, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N58" t="str">
+        <f>_xlfn.XLOOKUP(I58, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O58" t="str">
+        <f>_xlfn.XLOOKUP(I58, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>21231</v>
+      </c>
+      <c r="B59">
+        <v>336</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59">
+        <v>11122</v>
+      </c>
+      <c r="K59" t="str">
+        <f>_xlfn.XLOOKUP(I59, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L59" t="str">
+        <f>_xlfn.XLOOKUP(I59, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M59" t="str">
+        <f>_xlfn.XLOOKUP(I59, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N59" t="str">
+        <f>_xlfn.XLOOKUP(I59, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O59" t="str">
+        <f>_xlfn.XLOOKUP(I59, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>22112</v>
+      </c>
+      <c r="B60">
+        <v>182</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60">
+        <v>22112</v>
+      </c>
+      <c r="K60" t="str">
+        <f>_xlfn.XLOOKUP(I60, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L60" t="str">
+        <f>_xlfn.XLOOKUP(I60, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M60" t="str">
+        <f>_xlfn.XLOOKUP(I60, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N60" t="str">
+        <f>_xlfn.XLOOKUP(I60, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O60" t="str">
+        <f>_xlfn.XLOOKUP(I60, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>13122</v>
+      </c>
+      <c r="B61">
+        <v>273</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61">
+        <v>13122</v>
+      </c>
+      <c r="K61" t="str">
+        <f>_xlfn.XLOOKUP(I61, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L61" t="str">
+        <f>_xlfn.XLOOKUP(I61, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M61" t="str">
+        <f>_xlfn.XLOOKUP(I61, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N61" t="str">
+        <f>_xlfn.XLOOKUP(I61, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O61" t="str">
+        <f>_xlfn.XLOOKUP(I61, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>11222</v>
+      </c>
+      <c r="B62">
+        <v>410</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62">
+        <v>11222</v>
+      </c>
+      <c r="K62" t="str">
+        <f>_xlfn.XLOOKUP(I62, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L62" t="str">
+        <f>_xlfn.XLOOKUP(I62, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M62" t="str">
+        <f>_xlfn.XLOOKUP(I62, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N62" t="str">
+        <f>_xlfn.XLOOKUP(I62, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O62" t="str">
+        <f>_xlfn.XLOOKUP(I62, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>23111</v>
+      </c>
+      <c r="B63">
+        <v>63</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63">
+        <v>22221</v>
+      </c>
+      <c r="K63" t="str">
+        <f>_xlfn.XLOOKUP(I63, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L63" t="str">
+        <f>_xlfn.XLOOKUP(I63, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M63" t="str">
+        <f>_xlfn.XLOOKUP(I63, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N63" t="str">
+        <f>_xlfn.XLOOKUP(I63, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O63" t="str">
+        <f>_xlfn.XLOOKUP(I63, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>22221</v>
+      </c>
+      <c r="B64">
+        <v>171</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64">
+        <v>23111</v>
+      </c>
+      <c r="K64" t="str">
+        <f>_xlfn.XLOOKUP(I64, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L64" t="str">
+        <f>_xlfn.XLOOKUP(I64, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M64" t="str">
+        <f>_xlfn.XLOOKUP(I64, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N64" t="str">
+        <f>_xlfn.XLOOKUP(I64, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O64" t="str">
+        <f>_xlfn.XLOOKUP(I64, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>23231</v>
+      </c>
+      <c r="B65">
+        <v>249</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65">
+        <v>23132</v>
+      </c>
+      <c r="K65" t="str">
+        <f>_xlfn.XLOOKUP(I65, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L65" t="str">
+        <f>_xlfn.XLOOKUP(I65, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M65" t="str">
+        <f>_xlfn.XLOOKUP(I65, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N65" t="str">
+        <f>_xlfn.XLOOKUP(I65, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O65" t="str">
+        <f>_xlfn.XLOOKUP(I65, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>23132</v>
+      </c>
+      <c r="B66">
+        <v>470</v>
+      </c>
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66">
+        <v>23222</v>
+      </c>
+      <c r="K66" t="str">
+        <f>_xlfn.XLOOKUP(I66, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L66" t="str">
+        <f>_xlfn.XLOOKUP(I66, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M66" t="str">
+        <f>_xlfn.XLOOKUP(I66, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N66" t="str">
+        <f>_xlfn.XLOOKUP(I66, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O66" t="str">
+        <f>_xlfn.XLOOKUP(I66, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>23222</v>
+      </c>
+      <c r="B67">
+        <v>351</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67">
+        <v>23231</v>
+      </c>
+      <c r="K67" t="str">
+        <f>_xlfn.XLOOKUP(I67, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L67" t="str">
+        <f>_xlfn.XLOOKUP(I67, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M67" t="str">
+        <f>_xlfn.XLOOKUP(I67, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N67" t="str">
+        <f>_xlfn.XLOOKUP(I67, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O67" t="str">
+        <f>_xlfn.XLOOKUP(I67, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>11231</v>
+      </c>
+      <c r="B68">
+        <v>344</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68">
+        <v>11231</v>
+      </c>
+      <c r="K68" t="str">
+        <f>_xlfn.XLOOKUP(I68, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L68" t="str">
+        <f>_xlfn.XLOOKUP(I68, A2:A73, D2:D73)</f>
+        <v>6–9 years</v>
+      </c>
+      <c r="M68" t="str">
+        <f>_xlfn.XLOOKUP(I68, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N68" t="str">
+        <f>_xlfn.XLOOKUP(I68, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O68" t="str">
+        <f>_xlfn.XLOOKUP(I68, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>23232</v>
+      </c>
+      <c r="B69" s="2">
+        <v>503</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69">
+        <v>23232</v>
+      </c>
+      <c r="K69" t="str">
+        <f>_xlfn.XLOOKUP(I69, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L69" t="str">
+        <f>_xlfn.XLOOKUP(I69, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M69" t="str">
+        <f>_xlfn.XLOOKUP(I69, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N69" t="str">
+        <f>_xlfn.XLOOKUP(I69, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O69" t="str">
+        <f>_xlfn.XLOOKUP(I69, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>12221</v>
+      </c>
+      <c r="B70" s="2">
+        <v>204</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70">
+        <v>12221</v>
+      </c>
+      <c r="K70" t="str">
+        <f>_xlfn.XLOOKUP(I70, A2:A73, C2:C73)</f>
+        <v>Boys</v>
+      </c>
+      <c r="L70" t="str">
+        <f>_xlfn.XLOOKUP(I70, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M70" t="str">
+        <f>_xlfn.XLOOKUP(I70, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N70" t="str">
+        <f>_xlfn.XLOOKUP(I70, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O70" t="str">
+        <f>_xlfn.XLOOKUP(I70, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>22231</v>
+      </c>
+      <c r="B71" s="2">
+        <v>282</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71">
+        <v>22231</v>
+      </c>
+      <c r="K71" t="str">
+        <f>_xlfn.XLOOKUP(I71, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L71" t="str">
+        <f>_xlfn.XLOOKUP(I71, A2:A73, D2:D73)</f>
+        <v>10–12 years</v>
+      </c>
+      <c r="M71" t="str">
+        <f>_xlfn.XLOOKUP(I71, A2:A73, E2:E73)</f>
+        <v>Urban</v>
+      </c>
+      <c r="N71" t="str">
+        <f>_xlfn.XLOOKUP(I71, A2:A73, F2:F73)</f>
+        <v>Manual Workers</v>
+      </c>
+      <c r="O71" t="str">
+        <f>_xlfn.XLOOKUP(I71, A2:A73, G2:G73)</f>
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>23112</v>
+      </c>
+      <c r="B72" s="2">
+        <v>195</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72">
+        <v>23112</v>
+      </c>
+      <c r="K72" t="str">
+        <f>_xlfn.XLOOKUP(I72, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L72" t="str">
+        <f>_xlfn.XLOOKUP(I72, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M72" t="str">
+        <f>_xlfn.XLOOKUP(I72, A2:A73, E2:E73)</f>
+        <v>Rural</v>
+      </c>
+      <c r="N72" t="str">
+        <f>_xlfn.XLOOKUP(I72, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O72" t="str">
+        <f>_xlfn.XLOOKUP(I72, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>23122</v>
+      </c>
+      <c r="B73" s="2">
+        <v>246</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73">
+        <v>23122</v>
+      </c>
+      <c r="K73" t="str">
+        <f>_xlfn.XLOOKUP(I73, A2:A73, C2:C73)</f>
+        <v>Girls</v>
+      </c>
+      <c r="L73" t="str">
+        <f>_xlfn.XLOOKUP(I73, A2:A73, D2:D73)</f>
+        <v>13–15 years</v>
+      </c>
+      <c r="M73" t="str">
+        <f>_xlfn.XLOOKUP(I73, A2:A73, E2:E73)</f>
+        <v>Semi-urban</v>
+      </c>
+      <c r="N73" t="str">
+        <f>_xlfn.XLOOKUP(I73, A2:A73, F2:F73)</f>
+        <v>Non-Manual Workers</v>
+      </c>
+      <c r="O73" t="str">
+        <f>_xlfn.XLOOKUP(I73, A2:A73, G2:G73)</f>
+        <v>Pre</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>